--- a/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
+++ b/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
@@ -7,18 +7,19 @@
     <workbookView windowHeight="14860"/>
   </bookViews>
   <sheets>
-    <sheet name="任务列表 (9)" sheetId="11" r:id="rId1"/>
-    <sheet name="任务列表 (7)" sheetId="9" r:id="rId2"/>
-    <sheet name="任务列表 (10)" sheetId="12" r:id="rId3"/>
-    <sheet name="任务列表 (4)" sheetId="7" r:id="rId4"/>
-    <sheet name="任务列表 (8)" sheetId="10" r:id="rId5"/>
-    <sheet name="任务列表 (6)" sheetId="8" r:id="rId6"/>
-    <sheet name="任务列表 (5)" sheetId="6" r:id="rId7"/>
-    <sheet name="老剧" sheetId="5" r:id="rId8"/>
-    <sheet name="任务列表 (3)" sheetId="4" r:id="rId9"/>
-    <sheet name="任务列表" sheetId="1" r:id="rId10"/>
-    <sheet name="任务列表 (2)" sheetId="3" r:id="rId11"/>
-    <sheet name="字段说明" sheetId="2" r:id="rId12"/>
+    <sheet name="任务列表 (11)" sheetId="13" r:id="rId1"/>
+    <sheet name="任务列表 (9)" sheetId="11" r:id="rId2"/>
+    <sheet name="任务列表 (7)" sheetId="9" r:id="rId3"/>
+    <sheet name="任务列表 (10)" sheetId="12" r:id="rId4"/>
+    <sheet name="任务列表 (4)" sheetId="7" r:id="rId5"/>
+    <sheet name="任务列表 (8)" sheetId="10" r:id="rId6"/>
+    <sheet name="任务列表 (6)" sheetId="8" r:id="rId7"/>
+    <sheet name="任务列表 (5)" sheetId="6" r:id="rId8"/>
+    <sheet name="老剧" sheetId="5" r:id="rId9"/>
+    <sheet name="任务列表 (3)" sheetId="4" r:id="rId10"/>
+    <sheet name="任务列表" sheetId="1" r:id="rId11"/>
+    <sheet name="任务列表 (2)" sheetId="3" r:id="rId12"/>
+    <sheet name="字段说明" sheetId="2" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="451">
   <si>
     <t>任务</t>
   </si>
@@ -118,6 +119,297 @@
     <t>C-印尼-0316</t>
   </si>
   <si>
+    <t>你说我是废物-IDN</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-1</t>
+  </si>
+  <si>
+    <t>你说我是废物</t>
+  </si>
+  <si>
+    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>18+</t>
+  </si>
+  <si>
+    <t>Drama World</t>
+  </si>
+  <si>
+    <t>7620639348983136257</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-2</t>
+  </si>
+  <si>
+    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
+  </si>
+  <si>
+    <t>7620639323532214288</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-3</t>
+  </si>
+  <si>
+    <t>7620639335699709953</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-4</t>
+  </si>
+  <si>
+    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
+  </si>
+  <si>
+    <t>7620639354238566416</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-5</t>
+  </si>
+  <si>
+    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
+  </si>
+  <si>
+    <t>7620639304687222801</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-6</t>
+  </si>
+  <si>
+    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
+  </si>
+  <si>
+    <t>7620639323754627073</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-7</t>
+  </si>
+  <si>
+    <t>7620639340554387457</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-你说我是废物-2.5W-8</t>
+  </si>
+  <si>
+    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
+  </si>
+  <si>
+    <t>7621133797177901057</t>
+  </si>
+  <si>
+    <t>THA-低-C</t>
+  </si>
+  <si>
+    <t>你说我是废物-THAI</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-1</t>
+  </si>
+  <si>
+    <t>ph-1,hmj-1,MX2</t>
+  </si>
+  <si>
+    <t>7621133783397122065</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-2</t>
+  </si>
+  <si>
+    <t>ph-2,hmj-2,MX3</t>
+  </si>
+  <si>
+    <t>7621133859173974017</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-3</t>
+  </si>
+  <si>
+    <t>ph-3,hmj-3,wz-5</t>
+  </si>
+  <si>
+    <t>7621133806296383505</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-4</t>
+  </si>
+  <si>
+    <t>wz1,wz2,wz3</t>
+  </si>
+  <si>
+    <t>7621133840274341905</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-5</t>
+  </si>
+  <si>
+    <t>zyf-1,hsx-1,zzz泰国1</t>
+  </si>
+  <si>
+    <t>7621133873234673665</t>
+  </si>
+  <si>
+    <t>C-GF-xd-你说我是废物-49T-S+tr-xd-6</t>
+  </si>
+  <si>
+    <t>zzz泰国3,hsx-2,wz-7</t>
+  </si>
+  <si>
+    <t>团宠新生-IDN</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-1</t>
+  </si>
+  <si>
+    <t>团宠新生</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-2</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-3</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-4</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-5</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-6</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-7</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-团宠新生-2.5W-8</t>
+  </si>
+  <si>
+    <t>团宠新生-THAI</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-1</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-2</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-3</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-4</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-5</t>
+  </si>
+  <si>
+    <t>C-GF-xd-团宠新生-49T-S+tr-xd-6</t>
+  </si>
+  <si>
+    <t>迎着光的未来-IDN</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-1</t>
+  </si>
+  <si>
+    <t>迎着光的未来</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-2</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-3</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-4</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-5</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-6</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-7</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-迎着光的未来-2.5W-8</t>
+  </si>
+  <si>
+    <t>迎着光的未来-THAI</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-1</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-2</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-3</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-4</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-5</t>
+  </si>
+  <si>
+    <t>C-GF-xd-迎着光的未来-49T-S+tr-xd-6</t>
+  </si>
+  <si>
+    <t>掌上明主-IDN</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-1</t>
+  </si>
+  <si>
+    <t>掌上明主</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-2</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-3</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-4</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-5</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-6</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-7</t>
+  </si>
+  <si>
+    <t>C-GF-IDN-xd-掌上明主-2.5W-8</t>
+  </si>
+  <si>
+    <t>掌上明主-THAI</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-1</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-2</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-3</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-4</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-5</t>
+  </si>
+  <si>
+    <t>C-GF-xd-掌上明主-49T-S+tr-xd-6</t>
+  </si>
+  <si>
     <t>乔阳似火-IDN</t>
   </si>
   <si>
@@ -127,133 +419,46 @@
     <t>乔阳似火</t>
   </si>
   <si>
-    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
-  </si>
-  <si>
-    <t>价值</t>
-  </si>
-  <si>
-    <t>18+</t>
-  </si>
-  <si>
-    <t>Drama World</t>
-  </si>
-  <si>
-    <t>7620639348983136257</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-2</t>
   </si>
   <si>
-    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
-  </si>
-  <si>
-    <t>7620639323532214288</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-3</t>
   </si>
   <si>
-    <t>7620639335699709953</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-4</t>
   </si>
   <si>
-    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
-  </si>
-  <si>
-    <t>7620639354238566416</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-5</t>
   </si>
   <si>
-    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
-  </si>
-  <si>
-    <t>7620639304687222801</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-6</t>
   </si>
   <si>
-    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
-  </si>
-  <si>
-    <t>7620639323754627073</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-7</t>
   </si>
   <si>
-    <t>7620639340554387457</t>
-  </si>
-  <si>
     <t>C-GF-IDN-xd-乔阳似火-2.5W-8</t>
   </si>
   <si>
-    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
-  </si>
-  <si>
-    <t>7621133797177901057</t>
-  </si>
-  <si>
-    <t>THA-低-C</t>
-  </si>
-  <si>
     <t>乔阳似火-THAI</t>
   </si>
   <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-1</t>
   </si>
   <si>
-    <t>ph-1,hmj-1,MX2</t>
-  </si>
-  <si>
-    <t>7621133783397122065</t>
-  </si>
-  <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-2</t>
   </si>
   <si>
-    <t>ph-2,hmj-2,MX3</t>
-  </si>
-  <si>
-    <t>7621133859173974017</t>
-  </si>
-  <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-3</t>
   </si>
   <si>
-    <t>ph-3,hmj-3,wz-5</t>
-  </si>
-  <si>
-    <t>7621133806296383505</t>
-  </si>
-  <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-4</t>
   </si>
   <si>
-    <t>wz1,wz2,wz3</t>
-  </si>
-  <si>
-    <t>7621133840274341905</t>
-  </si>
-  <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-5</t>
   </si>
   <si>
-    <t>zyf-1,hsx-1,zzz泰国1</t>
-  </si>
-  <si>
-    <t>7621133873234673665</t>
-  </si>
-  <si>
     <t>C-GF-xd-乔阳似火-49T-S+tr-xd-6</t>
-  </si>
-  <si>
-    <t>zzz泰国3,hsx-2,wz-7</t>
   </si>
   <si>
     <t>鲁暗送秋波-IDN</t>
@@ -2395,13 +2600,13 @@
         <v>1.6</v>
       </c>
       <c r="N2" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O2" s="8">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="P2" s="9">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>31</v>
@@ -2418,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:23">
@@ -2651,13 +2856,13 @@
         <v>1.6</v>
       </c>
       <c r="N10" s="3">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O10" s="8">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="P10" s="9">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>31</v>
@@ -2674,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:23">
@@ -2823,37 +3028,81 @@
       <c r="W15" s="3"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:23">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="16"/>
+      <c r="A16" s="3">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="F16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="10"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+      <c r="H16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N16" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O16" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="U16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:23">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3">
+        <v>3</v>
+      </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="16" t="s">
+        <v>75</v>
+      </c>
       <c r="I17" s="10"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -2867,14 +3116,22 @@
       <c r="W17" s="3"/>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:23">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3">
+        <v>3</v>
+      </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="I18" s="10"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -2888,14 +3145,22 @@
       <c r="W18" s="3"/>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:23">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3">
+        <v>3</v>
+      </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
-      <c r="H19" s="16"/>
+      <c r="H19" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="I19" s="10"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -2909,14 +3174,22 @@
       <c r="W19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:23">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3">
+        <v>3</v>
+      </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="I20" s="10"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -2930,14 +3203,22 @@
       <c r="W20" s="3"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:23">
-      <c r="A21" s="3"/>
+      <c r="A21" s="3">
+        <v>3</v>
+      </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
-      <c r="H21" s="16"/>
+      <c r="H21" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="I21" s="10"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -2951,14 +3232,22 @@
       <c r="W21" s="3"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:23">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3">
+        <v>3</v>
+      </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="I22" s="10"/>
-      <c r="K22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -2972,14 +3261,22 @@
       <c r="W22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:23">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3">
+        <v>3</v>
+      </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="16" t="s">
+        <v>81</v>
+      </c>
       <c r="I23" s="10"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -2993,36 +3290,80 @@
       <c r="W23" s="3"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:23">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="10"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
+      <c r="A24" s="3">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O24" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
+      <c r="U24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:23">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3">
+        <v>4</v>
+      </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="12"/>
+      <c r="C25" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="I25" s="10"/>
-      <c r="K25" s="3"/>
+      <c r="K25" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3036,14 +3377,22 @@
       <c r="W25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:23">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3">
+        <v>4</v>
+      </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="12"/>
+      <c r="C26" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
-      <c r="H26" s="16"/>
+      <c r="H26" s="16" t="s">
+        <v>85</v>
+      </c>
       <c r="I26" s="10"/>
-      <c r="K26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -3057,14 +3406,22 @@
       <c r="W26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:23">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3">
+        <v>4</v>
+      </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="12"/>
+      <c r="C27" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="16" t="s">
+        <v>86</v>
+      </c>
       <c r="I27" s="10"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -3078,14 +3435,22 @@
       <c r="W27" s="3"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:23">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3">
+        <v>4</v>
+      </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="12"/>
+      <c r="C28" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
-      <c r="H28" s="16"/>
+      <c r="H28" s="16" t="s">
+        <v>87</v>
+      </c>
       <c r="I28" s="10"/>
-      <c r="K28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3099,14 +3464,22 @@
       <c r="W28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:23">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3">
+        <v>4</v>
+      </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="12"/>
+      <c r="C29" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
-      <c r="H29" s="16"/>
+      <c r="H29" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="I29" s="10"/>
-      <c r="K29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
@@ -3120,36 +3493,80 @@
       <c r="W29" s="3"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:23">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="6"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
+      <c r="A30" s="3">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N30" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O30" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
+      <c r="U30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:23">
-      <c r="A31" s="3"/>
+      <c r="A31" s="3">
+        <v>5</v>
+      </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
-      <c r="H31" s="16"/>
+      <c r="H31" s="16" t="s">
+        <v>92</v>
+      </c>
       <c r="I31" s="10"/>
-      <c r="K31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -3163,14 +3580,22 @@
       <c r="W31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:23">
-      <c r="A32" s="3"/>
+      <c r="A32" s="3">
+        <v>5</v>
+      </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="10"/>
-      <c r="H32" s="16"/>
+      <c r="H32" s="16" t="s">
+        <v>93</v>
+      </c>
       <c r="I32" s="10"/>
-      <c r="K32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L32" s="3"/>
       <c r="M32" s="5"/>
       <c r="N32" s="3"/>
@@ -3184,14 +3609,22 @@
       <c r="W32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:23">
-      <c r="A33" s="3"/>
+      <c r="A33" s="3">
+        <v>5</v>
+      </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="D33" s="5"/>
       <c r="E33" s="10"/>
-      <c r="H33" s="16"/>
+      <c r="H33" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="I33" s="10"/>
-      <c r="K33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
@@ -3205,14 +3638,22 @@
       <c r="W33" s="3"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:23">
-      <c r="A34" s="3"/>
+      <c r="A34" s="3">
+        <v>5</v>
+      </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="D34" s="5"/>
       <c r="E34" s="10"/>
-      <c r="H34" s="16"/>
+      <c r="H34" s="16" t="s">
+        <v>95</v>
+      </c>
       <c r="I34" s="10"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -3226,14 +3667,22 @@
       <c r="W34" s="3"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:23">
-      <c r="A35" s="3"/>
+      <c r="A35" s="3">
+        <v>5</v>
+      </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D35" s="5"/>
       <c r="E35" s="11"/>
-      <c r="H35" s="16"/>
+      <c r="H35" s="16" t="s">
+        <v>96</v>
+      </c>
       <c r="I35" s="10"/>
-      <c r="K35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
@@ -3247,14 +3696,22 @@
       <c r="W35" s="3"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:23">
-      <c r="A36" s="3"/>
+      <c r="A36" s="3">
+        <v>5</v>
+      </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="D36" s="5"/>
       <c r="E36" s="10"/>
-      <c r="H36" s="16"/>
+      <c r="H36" s="16" t="s">
+        <v>97</v>
+      </c>
       <c r="I36" s="10"/>
-      <c r="K36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
@@ -3268,14 +3725,22 @@
       <c r="W36" s="3"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:23">
-      <c r="A37" s="3"/>
+      <c r="A37" s="3">
+        <v>5</v>
+      </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D37" s="5"/>
       <c r="E37" s="10"/>
-      <c r="H37" s="16"/>
+      <c r="H37" s="16" t="s">
+        <v>98</v>
+      </c>
       <c r="I37" s="10"/>
-      <c r="K37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
@@ -3289,36 +3754,80 @@
       <c r="W37" s="3"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:23">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="6"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
+      <c r="A38" s="3">
+        <v>6</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N38" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O38" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
+      <c r="U38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:23">
-      <c r="A39" s="3"/>
+      <c r="A39" s="3">
+        <v>6</v>
+      </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="12"/>
+      <c r="C39" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="10"/>
-      <c r="H39" s="16"/>
+      <c r="H39" s="16" t="s">
+        <v>101</v>
+      </c>
       <c r="I39" s="10"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
@@ -3332,14 +3841,22 @@
       <c r="V39" s="3"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:23">
-      <c r="A40" s="3"/>
+      <c r="A40" s="3">
+        <v>6</v>
+      </c>
       <c r="B40" s="3"/>
-      <c r="C40" s="12"/>
+      <c r="C40" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="D40" s="3"/>
       <c r="E40" s="10"/>
-      <c r="H40" s="16"/>
+      <c r="H40" s="16" t="s">
+        <v>102</v>
+      </c>
       <c r="I40" s="10"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -3353,14 +3870,22 @@
       <c r="V40" s="3"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:23">
-      <c r="A41" s="3"/>
+      <c r="A41" s="3">
+        <v>6</v>
+      </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="12"/>
+      <c r="C41" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="D41" s="3"/>
       <c r="E41" s="10"/>
-      <c r="H41" s="16"/>
+      <c r="H41" s="16" t="s">
+        <v>103</v>
+      </c>
       <c r="I41" s="10"/>
-      <c r="K41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
@@ -3374,14 +3899,22 @@
       <c r="V41" s="3"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:23">
-      <c r="A42" s="3"/>
+      <c r="A42" s="3">
+        <v>6</v>
+      </c>
       <c r="B42" s="3"/>
-      <c r="C42" s="12"/>
+      <c r="C42" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="10"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="16" t="s">
+        <v>104</v>
+      </c>
       <c r="I42" s="10"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
@@ -3395,14 +3928,22 @@
       <c r="V42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:23">
-      <c r="A43" s="3"/>
+      <c r="A43" s="3">
+        <v>6</v>
+      </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="12"/>
+      <c r="C43" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="D43" s="3"/>
       <c r="E43" s="10"/>
-      <c r="H43" s="16"/>
+      <c r="H43" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="I43" s="10"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
@@ -3416,36 +3957,80 @@
       <c r="V43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:23">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="6"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
+      <c r="A44" s="3">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O44" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
+      <c r="U44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W44" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:23">
-      <c r="A45" s="3"/>
+      <c r="A45" s="3">
+        <v>7</v>
+      </c>
       <c r="B45" s="3"/>
-      <c r="C45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D45" s="5"/>
       <c r="E45" s="10"/>
-      <c r="H45" s="16"/>
+      <c r="H45" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="I45" s="10"/>
-      <c r="K45" s="3"/>
+      <c r="K45" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
@@ -3459,14 +4044,22 @@
       <c r="W45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:23">
-      <c r="A46" s="3"/>
+      <c r="A46" s="3">
+        <v>7</v>
+      </c>
       <c r="B46" s="3"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D46" s="5"/>
       <c r="E46" s="10"/>
-      <c r="H46" s="16"/>
+      <c r="H46" s="16" t="s">
+        <v>110</v>
+      </c>
       <c r="I46" s="10"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -3480,14 +4073,22 @@
       <c r="W46" s="3"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:23">
-      <c r="A47" s="3"/>
+      <c r="A47" s="3">
+        <v>7</v>
+      </c>
       <c r="B47" s="3"/>
-      <c r="C47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="D47" s="5"/>
       <c r="E47" s="10"/>
-      <c r="H47" s="16"/>
+      <c r="H47" s="16" t="s">
+        <v>111</v>
+      </c>
       <c r="I47" s="10"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
@@ -3501,14 +4102,22 @@
       <c r="W47" s="3"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:23">
-      <c r="A48" s="3"/>
+      <c r="A48" s="3">
+        <v>7</v>
+      </c>
       <c r="B48" s="3"/>
-      <c r="C48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="D48" s="5"/>
       <c r="E48" s="10"/>
-      <c r="H48" s="16"/>
+      <c r="H48" s="16" t="s">
+        <v>112</v>
+      </c>
       <c r="I48" s="10"/>
-      <c r="K48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -3522,14 +4131,22 @@
       <c r="W48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:23">
-      <c r="A49" s="3"/>
+      <c r="A49" s="3">
+        <v>7</v>
+      </c>
       <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
-      <c r="H49" s="16"/>
+      <c r="H49" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="I49" s="10"/>
-      <c r="K49" s="3"/>
+      <c r="K49" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -3543,14 +4160,22 @@
       <c r="W49" s="3"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:23">
-      <c r="A50" s="3"/>
+      <c r="A50" s="3">
+        <v>7</v>
+      </c>
       <c r="B50" s="3"/>
-      <c r="C50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="D50" s="5"/>
       <c r="E50" s="10"/>
-      <c r="H50" s="16"/>
+      <c r="H50" s="16" t="s">
+        <v>114</v>
+      </c>
       <c r="I50" s="10"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -3564,14 +4189,22 @@
       <c r="W50" s="3"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:23">
-      <c r="A51" s="3"/>
+      <c r="A51" s="3">
+        <v>7</v>
+      </c>
       <c r="B51" s="3"/>
-      <c r="C51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D51" s="5"/>
       <c r="E51" s="10"/>
-      <c r="H51" s="16"/>
+      <c r="H51" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="I51" s="10"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -3585,36 +4218,80 @@
       <c r="W51" s="3"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:23">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="6"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
+      <c r="A52" s="3">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M52" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O52" s="8">
+        <v>46121</v>
+      </c>
+      <c r="P52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
+      <c r="U52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W52" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:23">
-      <c r="A53" s="3"/>
+      <c r="A53" s="3">
+        <v>8</v>
+      </c>
       <c r="B53" s="3"/>
-      <c r="C53" s="12"/>
+      <c r="C53" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D53" s="3"/>
       <c r="E53" s="10"/>
-      <c r="H53" s="16"/>
+      <c r="H53" s="16" t="s">
+        <v>118</v>
+      </c>
       <c r="I53" s="10"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
@@ -3628,14 +4305,22 @@
       <c r="W53" s="3"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:23">
-      <c r="A54" s="3"/>
+      <c r="A54" s="3">
+        <v>8</v>
+      </c>
       <c r="B54" s="3"/>
-      <c r="C54" s="12"/>
+      <c r="C54" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="10"/>
-      <c r="H54" s="16"/>
+      <c r="H54" s="16" t="s">
+        <v>119</v>
+      </c>
       <c r="I54" s="10"/>
-      <c r="K54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -3649,14 +4334,22 @@
       <c r="W54" s="3"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:23">
-      <c r="A55" s="3"/>
+      <c r="A55" s="3">
+        <v>8</v>
+      </c>
       <c r="B55" s="3"/>
-      <c r="C55" s="12"/>
+      <c r="C55" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="10"/>
-      <c r="H55" s="16"/>
+      <c r="H55" s="16" t="s">
+        <v>120</v>
+      </c>
       <c r="I55" s="10"/>
-      <c r="K55" s="3"/>
+      <c r="K55" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
@@ -3670,14 +4363,22 @@
       <c r="W55" s="3"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:23">
-      <c r="A56" s="3"/>
+      <c r="A56" s="3">
+        <v>8</v>
+      </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="12"/>
+      <c r="C56" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="10"/>
-      <c r="H56" s="16"/>
+      <c r="H56" s="16" t="s">
+        <v>121</v>
+      </c>
       <c r="I56" s="10"/>
-      <c r="K56" s="3"/>
+      <c r="K56" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
@@ -3691,14 +4392,22 @@
       <c r="W56" s="3"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:23">
-      <c r="A57" s="3"/>
+      <c r="A57" s="3">
+        <v>8</v>
+      </c>
       <c r="B57" s="3"/>
-      <c r="C57" s="12"/>
+      <c r="C57" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="11"/>
-      <c r="H57" s="16"/>
+      <c r="H57" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="I57" s="10"/>
-      <c r="K57" s="3"/>
+      <c r="K57" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
@@ -4014,6 +4723,575 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
+    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="16.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="10.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="9.51785714285714" customWidth="1"/>
+    <col min="8" max="8" width="33.1875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.8303571428571" customWidth="1"/>
+    <col min="10" max="10" width="22.8303571428571" customWidth="1"/>
+    <col min="11" max="11" width="35.8303571428571" customWidth="1"/>
+    <col min="12" max="12" width="10.8303571428571" customWidth="1"/>
+    <col min="13" max="14" width="8.83035714285714" customWidth="1"/>
+    <col min="15" max="15" width="12.8303571428571" customWidth="1"/>
+    <col min="16" max="16" width="10.8303571428571" customWidth="1"/>
+    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
+    <col min="18" max="20" width="10.8303571428571" customWidth="1"/>
+    <col min="21" max="21" width="8.83035714285714" customWidth="1"/>
+    <col min="22" max="22" width="18.8303571428571" customWidth="1"/>
+    <col min="23" max="23" width="10.8303571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:23">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="N2" s="3">
+        <v>500</v>
+      </c>
+      <c r="O2" s="8">
+        <v>46116</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:23">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="10"/>
+      <c r="H3" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="K3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:23">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="10"/>
+      <c r="H4" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="K4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:23">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="10"/>
+      <c r="H5" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="K5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="W5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:23">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="10"/>
+      <c r="H6" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="K6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="W6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:23">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="11"/>
+      <c r="H7" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="K7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="W7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:23">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="10"/>
+      <c r="H8" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="K8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:23">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="10"/>
+      <c r="H9" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="K9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:23">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="N10" s="3">
+        <v>500</v>
+      </c>
+      <c r="O10" s="8">
+        <v>46116</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:23">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="10"/>
+      <c r="H11" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="K11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:23">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="10"/>
+      <c r="H12" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="K12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:23">
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="10"/>
+      <c r="H13" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="K13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="W13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:23">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="10"/>
+      <c r="H14" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="K14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="W14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:23">
+      <c r="A15" s="3">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="11"/>
+      <c r="H15" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="K15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="W15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W29"/>
@@ -4126,13 +5404,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -4181,7 +5459,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="10"/>
       <c r="H3" s="14" t="s">
-        <v>269</v>
+        <v>337</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -4210,7 +5488,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="10"/>
       <c r="H4" s="14" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -4239,7 +5517,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="10"/>
       <c r="H5" s="14" t="s">
-        <v>271</v>
+        <v>339</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -4268,7 +5546,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="10"/>
       <c r="H6" s="14" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -4297,7 +5575,7 @@
       <c r="D7" s="5"/>
       <c r="E7" s="11"/>
       <c r="H7" s="14" t="s">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -4326,7 +5604,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="14" t="s">
-        <v>274</v>
+        <v>342</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -4355,7 +5633,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="14" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -4387,13 +5665,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -4442,7 +5720,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="15" t="s">
-        <v>278</v>
+        <v>346</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -4471,7 +5749,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="15" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -4500,7 +5778,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="15" t="s">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -4529,7 +5807,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="15" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -4558,7 +5836,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="15" t="s">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -4590,13 +5868,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -4645,7 +5923,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="14" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -4674,7 +5952,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="14" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -4703,7 +5981,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="14" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -4732,7 +6010,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="14" t="s">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -4761,7 +6039,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="14" t="s">
-        <v>290</v>
+        <v>358</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -4790,7 +6068,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="14" t="s">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -4819,7 +6097,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="14" t="s">
-        <v>292</v>
+        <v>360</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -4851,13 +6129,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -4906,7 +6184,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="15" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -4935,7 +6213,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="15" t="s">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -4964,7 +6242,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="15" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -4993,7 +6271,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="15" t="s">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -5022,7 +6300,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="15" t="s">
-        <v>299</v>
+        <v>367</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -5049,7 +6327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W43"/>
@@ -5162,13 +6440,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>300</v>
+        <v>368</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>301</v>
+        <v>369</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -5217,7 +6495,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="10"/>
       <c r="H3" s="7" t="s">
-        <v>303</v>
+        <v>371</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -5246,7 +6524,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="10"/>
       <c r="H4" s="7" t="s">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -5275,7 +6553,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="10"/>
       <c r="H5" s="7" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -5304,7 +6582,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="10"/>
       <c r="H6" s="7" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -5333,7 +6611,7 @@
       <c r="D7" s="5"/>
       <c r="E7" s="11"/>
       <c r="H7" s="7" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -5362,7 +6640,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="7" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -5391,7 +6669,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="7" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -5423,13 +6701,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>310</v>
+        <v>378</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -5478,7 +6756,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="13" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -5507,7 +6785,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="13" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -5536,7 +6814,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="13" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -5565,7 +6843,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="13" t="s">
-        <v>315</v>
+        <v>383</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -5594,7 +6872,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="13" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -5626,13 +6904,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -5681,7 +6959,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="14" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -5710,7 +6988,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="14" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -5739,7 +7017,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="14" t="s">
-        <v>253</v>
+        <v>321</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -5768,7 +7046,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="14" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -5797,7 +7075,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="14" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -5826,7 +7104,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="14" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -5855,7 +7133,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="14" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -5887,13 +7165,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>258</v>
+        <v>326</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -5942,7 +7220,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="13" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -5971,7 +7249,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="13" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -6000,7 +7278,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="13" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -6029,7 +7307,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="13" t="s">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -6058,7 +7336,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="13" t="s">
-        <v>265</v>
+        <v>333</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -6090,13 +7368,13 @@
         <v>25</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>319</v>
+        <v>387</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>29</v>
@@ -6145,7 +7423,7 @@
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
       <c r="H31" s="14" t="s">
-        <v>320</v>
+        <v>388</v>
       </c>
       <c r="I31" s="10"/>
       <c r="K31" s="3" t="s">
@@ -6174,7 +7452,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="10"/>
       <c r="H32" s="14" t="s">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="I32" s="10"/>
       <c r="K32" s="3" t="s">
@@ -6203,7 +7481,7 @@
       <c r="D33" s="5"/>
       <c r="E33" s="10"/>
       <c r="H33" s="14" t="s">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="I33" s="10"/>
       <c r="K33" s="3" t="s">
@@ -6232,7 +7510,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="10"/>
       <c r="H34" s="14" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="I34" s="10"/>
       <c r="K34" s="3" t="s">
@@ -6261,7 +7539,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="11"/>
       <c r="H35" s="14" t="s">
-        <v>324</v>
+        <v>392</v>
       </c>
       <c r="I35" s="10"/>
       <c r="K35" s="3" t="s">
@@ -6290,7 +7568,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="10"/>
       <c r="H36" s="14" t="s">
-        <v>325</v>
+        <v>393</v>
       </c>
       <c r="I36" s="10"/>
       <c r="K36" s="3" t="s">
@@ -6319,7 +7597,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="10"/>
       <c r="H37" s="14" t="s">
-        <v>326</v>
+        <v>394</v>
       </c>
       <c r="I37" s="10"/>
       <c r="K37" s="3" t="s">
@@ -6351,13 +7629,13 @@
         <v>53</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>319</v>
+        <v>387</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>56</v>
@@ -6406,7 +7684,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="10"/>
       <c r="H39" s="13" t="s">
-        <v>329</v>
+        <v>397</v>
       </c>
       <c r="I39" s="10"/>
       <c r="K39" s="3" t="s">
@@ -6435,7 +7713,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="10"/>
       <c r="H40" s="13" t="s">
-        <v>330</v>
+        <v>398</v>
       </c>
       <c r="I40" s="10"/>
       <c r="K40" s="3" t="s">
@@ -6464,7 +7742,7 @@
       <c r="D41" s="3"/>
       <c r="E41" s="10"/>
       <c r="H41" s="13" t="s">
-        <v>331</v>
+        <v>399</v>
       </c>
       <c r="I41" s="10"/>
       <c r="K41" s="3" t="s">
@@ -6493,7 +7771,7 @@
       <c r="D42" s="3"/>
       <c r="E42" s="10"/>
       <c r="H42" s="13" t="s">
-        <v>332</v>
+        <v>400</v>
       </c>
       <c r="I42" s="10"/>
       <c r="K42" s="3" t="s">
@@ -6522,7 +7800,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="10"/>
       <c r="H43" s="13" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="I43" s="10"/>
       <c r="K43" s="3" t="s">
@@ -6546,7 +7824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D24"/>
@@ -6560,16 +7838,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
       <c r="C1" t="s">
-        <v>336</v>
+        <v>404</v>
       </c>
       <c r="D1" t="s">
-        <v>337</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6577,13 +7855,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6591,13 +7869,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6605,13 +7883,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>344</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="D4" t="s">
-        <v>345</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6619,13 +7897,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6633,13 +7911,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>348</v>
+        <v>416</v>
       </c>
       <c r="C6" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D6" t="s">
-        <v>349</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6647,13 +7925,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="D7" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6661,13 +7939,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="C8" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6675,13 +7953,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>356</v>
+        <v>424</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="D9" t="s">
-        <v>357</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6689,13 +7967,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>426</v>
       </c>
       <c r="C10" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>359</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6703,13 +7981,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="C11" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D11" t="s">
-        <v>361</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6717,13 +7995,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>362</v>
+        <v>430</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D12" t="s">
-        <v>363</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6731,10 +8009,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>432</v>
       </c>
       <c r="C13" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -6745,13 +8023,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="C14" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D14" t="s">
-        <v>366</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6759,13 +8037,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="C15" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D15" t="s">
-        <v>368</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6773,13 +8051,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>369</v>
+        <v>437</v>
       </c>
       <c r="C16" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6787,13 +8065,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="C17" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D17" t="s">
-        <v>372</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -6801,10 +8079,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>373</v>
+        <v>441</v>
       </c>
       <c r="C18" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -6815,13 +8093,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>374</v>
+        <v>442</v>
       </c>
       <c r="C19" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6829,13 +8107,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>443</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="D20" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6843,13 +8121,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="C21" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="D21" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -6857,13 +8135,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="C22" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6871,13 +8149,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="C23" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="D23" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6885,13 +8163,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>381</v>
+        <v>449</v>
       </c>
       <c r="C24" t="s">
-        <v>351</v>
+        <v>419</v>
       </c>
       <c r="D24" t="s">
-        <v>382</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -6904,6 +8182,1755 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:W71"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
+    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="16.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="10.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="9.51785714285714" customWidth="1"/>
+    <col min="8" max="8" width="33.1875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.8303571428571" customWidth="1"/>
+    <col min="10" max="10" width="22.8303571428571" customWidth="1"/>
+    <col min="11" max="11" width="35.8303571428571" customWidth="1"/>
+    <col min="12" max="12" width="10.8303571428571" customWidth="1"/>
+    <col min="13" max="14" width="8.83035714285714" customWidth="1"/>
+    <col min="15" max="15" width="12.8303571428571" customWidth="1"/>
+    <col min="16" max="16" width="10.8303571428571" customWidth="1"/>
+    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
+    <col min="18" max="20" width="10.8303571428571" customWidth="1"/>
+    <col min="21" max="21" width="8.83035714285714" customWidth="1"/>
+    <col min="22" max="22" width="18.8303571428571" customWidth="1"/>
+    <col min="23" max="23" width="10.8303571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:23">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N2" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O2" s="8">
+        <v>46120</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:23">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="H3" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="K3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="W3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:23">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="H4" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="K4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="W4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:23">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="H5" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="K5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="W5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:23">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="H6" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="K6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="W6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:23">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="H7" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="K7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="W7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:23">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="10"/>
+      <c r="H8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="K8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="W8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:23">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="10"/>
+      <c r="H9" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="K9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="W9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:23">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O10" s="8">
+        <v>46120</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:23">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="10"/>
+      <c r="H11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="K11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:23">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="10"/>
+      <c r="H12" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="K12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:23">
+      <c r="A13" s="3">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="10"/>
+      <c r="H13" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="K13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="W13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:23">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="10"/>
+      <c r="H14" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="K14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="W14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:23">
+      <c r="A15" s="3">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="11"/>
+      <c r="H15" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="K15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="W15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:23">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="10"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:23">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="10"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="10"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="W17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:23">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="10"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="10"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="W18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:23">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="10"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="10"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:23">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="10"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="10"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="W20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:23">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="10"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="W21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:23">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="10"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="10"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="W22" s="3"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="10"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="10"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="W23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:23">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="10"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:23">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="10"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="10"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="W25" s="3"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:23">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="10"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="10"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="W26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:23">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="10"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="10"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="W27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:23">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="10"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="10"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="W28" s="3"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:23">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="11"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="10"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="W29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:23">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="6"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:23">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="10"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="10"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="W31" s="3"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:23">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="10"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="10"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="W32" s="3"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:23">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="10"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="10"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="W33" s="3"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:23">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="10"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="10"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="W34" s="3"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:23">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="11"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="10"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="W35" s="3"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:23">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="10"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="10"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="W36" s="3"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:23">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="10"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="10"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="W37" s="3"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:23">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="6"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:23">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="10"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="10"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:23">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="10"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="10"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:23">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="10"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="10"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:23">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="10"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="10"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:23">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="10"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="10"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:23">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="6"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:23">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="10"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="10"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="W45" s="3"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:23">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="10"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="10"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="W46" s="3"/>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:23">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="10"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="10"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="W47" s="3"/>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:23">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="10"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="10"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="W48" s="3"/>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:23">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="11"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="10"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="W49" s="3"/>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:23">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="10"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="10"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="W50" s="3"/>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:23">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="10"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="10"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="W51" s="3"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:23">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="6"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:23">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="10"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="10"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="W53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:23">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="10"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="10"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="W54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:23">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="10"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="10"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:23">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="10"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="10"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:23">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="11"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="10"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="W57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:23">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="10"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:23">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="10"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="10"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="W59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:23">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="10"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="10"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="W60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:23">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="10"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="10"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="W61" s="3"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:23">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="10"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="10"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="W62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:23">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="11"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="10"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="W63" s="3"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:23">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="10"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="10"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="W64" s="3"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:23">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="10"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="10"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="W65" s="3"/>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:23">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="10"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:23">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="10"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="10"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:23">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="10"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="10"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="W68" s="3"/>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:23">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="10"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="10"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="W69" s="3"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:23">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="10"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="10"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="W70" s="3"/>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:23">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="11"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="10"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="W71" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W23"/>
@@ -7016,13 +10043,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -7071,7 +10098,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="10"/>
       <c r="H3" s="16" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -7100,7 +10127,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="10"/>
       <c r="H4" s="16" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -7129,7 +10156,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="10"/>
       <c r="H5" s="16" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -7158,7 +10185,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="10"/>
       <c r="H6" s="16" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -7187,7 +10214,7 @@
       <c r="D7" s="5"/>
       <c r="E7" s="11"/>
       <c r="H7" s="16" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -7216,7 +10243,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="16" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -7245,7 +10272,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="16" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -7565,7 +10592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W71"/>
@@ -7678,13 +10705,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -7732,7 +10759,7 @@
       </c>
       <c r="D3" s="5"/>
       <c r="H3" s="16" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -7760,7 +10787,7 @@
       </c>
       <c r="D4" s="5"/>
       <c r="H4" s="16" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -7788,7 +10815,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="H5" s="16" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -7816,7 +10843,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="H6" s="16" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -7844,7 +10871,7 @@
       </c>
       <c r="D7" s="5"/>
       <c r="H7" s="16" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -7873,7 +10900,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="16" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -7902,7 +10929,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="16" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -7934,13 +10961,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -7989,7 +11016,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="16" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -8018,7 +11045,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="16" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -8047,7 +11074,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="16" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -8076,7 +11103,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="16" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -8105,7 +11132,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="16" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -8137,14 +11164,14 @@
         <v>25</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="F16" s="16"/>
       <c r="H16" s="16" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -8193,7 +11220,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="16" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -8222,7 +11249,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="16" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -8251,7 +11278,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="16" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -8280,7 +11307,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="16" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -8309,7 +11336,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="16" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -8338,7 +11365,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="16" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -8367,7 +11394,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="16" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -8399,13 +11426,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -8454,7 +11481,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="16" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -8483,7 +11510,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="16" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -8512,7 +11539,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="16" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -8541,7 +11568,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="16" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -8570,7 +11597,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="16" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -8602,13 +11629,13 @@
         <v>25</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>29</v>
@@ -8657,7 +11684,7 @@
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
       <c r="H31" s="16" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="I31" s="10"/>
       <c r="K31" s="3" t="s">
@@ -8686,7 +11713,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="10"/>
       <c r="H32" s="16" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="I32" s="10"/>
       <c r="K32" s="3" t="s">
@@ -8715,7 +11742,7 @@
       <c r="D33" s="5"/>
       <c r="E33" s="10"/>
       <c r="H33" s="16" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="I33" s="10"/>
       <c r="K33" s="3" t="s">
@@ -8744,7 +11771,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="10"/>
       <c r="H34" s="16" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="I34" s="10"/>
       <c r="K34" s="3" t="s">
@@ -8773,7 +11800,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="11"/>
       <c r="H35" s="16" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="I35" s="10"/>
       <c r="K35" s="3" t="s">
@@ -8802,7 +11829,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="10"/>
       <c r="H36" s="16" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="I36" s="10"/>
       <c r="K36" s="3" t="s">
@@ -8831,7 +11858,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="10"/>
       <c r="H37" s="16" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="I37" s="10"/>
       <c r="K37" s="3" t="s">
@@ -8863,13 +11890,13 @@
         <v>53</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>56</v>
@@ -8918,7 +11945,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="10"/>
       <c r="H39" s="16" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="I39" s="10"/>
       <c r="K39" s="3" t="s">
@@ -8947,7 +11974,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="10"/>
       <c r="H40" s="16" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="I40" s="10"/>
       <c r="K40" s="3" t="s">
@@ -8976,7 +12003,7 @@
       <c r="D41" s="3"/>
       <c r="E41" s="10"/>
       <c r="H41" s="16" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="I41" s="10"/>
       <c r="K41" s="3" t="s">
@@ -9005,7 +12032,7 @@
       <c r="D42" s="3"/>
       <c r="E42" s="10"/>
       <c r="H42" s="16" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="I42" s="10"/>
       <c r="K42" s="3" t="s">
@@ -9034,7 +12061,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="10"/>
       <c r="H43" s="16" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="I43" s="10"/>
       <c r="K43" s="3" t="s">
@@ -9066,13 +12093,13 @@
         <v>25</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>29</v>
@@ -9121,7 +12148,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="10"/>
       <c r="H45" s="16" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="I45" s="10"/>
       <c r="K45" s="3" t="s">
@@ -9150,7 +12177,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="10"/>
       <c r="H46" s="16" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="I46" s="10"/>
       <c r="K46" s="3" t="s">
@@ -9179,7 +12206,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="10"/>
       <c r="H47" s="16" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="I47" s="10"/>
       <c r="K47" s="3" t="s">
@@ -9208,7 +12235,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="10"/>
       <c r="H48" s="16" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="I48" s="10"/>
       <c r="K48" s="3" t="s">
@@ -9237,7 +12264,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
       <c r="H49" s="16" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="I49" s="10"/>
       <c r="K49" s="3" t="s">
@@ -9266,7 +12293,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="10"/>
       <c r="H50" s="16" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="I50" s="10"/>
       <c r="K50" s="3" t="s">
@@ -9295,7 +12322,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="10"/>
       <c r="H51" s="16" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="I51" s="10"/>
       <c r="K51" s="3" t="s">
@@ -9327,13 +12354,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>56</v>
@@ -9382,7 +12409,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="10"/>
       <c r="H53" s="16" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="I53" s="10"/>
       <c r="K53" s="3" t="s">
@@ -9411,7 +12438,7 @@
       <c r="D54" s="3"/>
       <c r="E54" s="10"/>
       <c r="H54" s="16" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="I54" s="10"/>
       <c r="K54" s="3" t="s">
@@ -9440,7 +12467,7 @@
       <c r="D55" s="3"/>
       <c r="E55" s="10"/>
       <c r="H55" s="16" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="I55" s="10"/>
       <c r="K55" s="3" t="s">
@@ -9469,7 +12496,7 @@
       <c r="D56" s="3"/>
       <c r="E56" s="10"/>
       <c r="H56" s="16" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="I56" s="10"/>
       <c r="K56" s="3" t="s">
@@ -9498,7 +12525,7 @@
       <c r="D57" s="3"/>
       <c r="E57" s="11"/>
       <c r="H57" s="16" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="I57" s="10"/>
       <c r="K57" s="3" t="s">
@@ -9818,7 +12845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W21"/>
@@ -9931,10 +12958,10 @@
         <v>25</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="I2" s="6"/>
       <c r="K2" s="3" t="s">
@@ -9983,7 +13010,7 @@
       </c>
       <c r="D3" s="5"/>
       <c r="H3" s="16" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -10011,7 +13038,7 @@
       </c>
       <c r="D4" s="5"/>
       <c r="H4" s="16" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -10039,7 +13066,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="H5" s="16" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -10072,7 +13099,7 @@
       </c>
       <c r="E6" s="14"/>
       <c r="H6" s="16" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -10597,7 +13624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W71"/>
@@ -10710,13 +13737,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -10764,7 +13791,7 @@
       </c>
       <c r="D3" s="5"/>
       <c r="H3" s="14" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -10792,7 +13819,7 @@
       </c>
       <c r="D4" s="5"/>
       <c r="H4" s="14" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -10820,7 +13847,7 @@
       </c>
       <c r="D5" s="5"/>
       <c r="H5" s="14" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -10848,7 +13875,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="H6" s="14" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -10876,7 +13903,7 @@
       </c>
       <c r="D7" s="5"/>
       <c r="H7" s="14" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -10905,7 +13932,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="14" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -10934,7 +13961,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="14" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -10966,13 +13993,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -11021,7 +14048,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="14" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -11050,7 +14077,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="14" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -11079,7 +14106,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="14" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -11108,7 +14135,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="14" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -11137,7 +14164,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="14" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -11169,13 +14196,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -11224,7 +14251,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="14" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -11253,7 +14280,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="14" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -11282,7 +14309,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="14" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -11311,7 +14338,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="14" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -11340,7 +14367,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="14" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -11369,7 +14396,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="14" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -11398,7 +14425,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="14" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -11430,13 +14457,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -11485,7 +14512,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="14" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -11514,7 +14541,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="14" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -11543,7 +14570,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="14" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -11572,7 +14599,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="14" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -11601,7 +14628,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="14" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -11633,13 +14660,13 @@
         <v>25</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>29</v>
@@ -11688,7 +14715,7 @@
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
       <c r="H31" s="14" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="I31" s="10"/>
       <c r="K31" s="3" t="s">
@@ -11717,7 +14744,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="10"/>
       <c r="H32" s="14" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="I32" s="10"/>
       <c r="K32" s="3" t="s">
@@ -11746,7 +14773,7 @@
       <c r="D33" s="5"/>
       <c r="E33" s="10"/>
       <c r="H33" s="14" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="I33" s="10"/>
       <c r="K33" s="3" t="s">
@@ -11775,7 +14802,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="10"/>
       <c r="H34" s="14" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="I34" s="10"/>
       <c r="K34" s="3" t="s">
@@ -11804,7 +14831,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="11"/>
       <c r="H35" s="14" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="I35" s="10"/>
       <c r="K35" s="3" t="s">
@@ -11833,7 +14860,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="10"/>
       <c r="H36" s="14" t="s">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="I36" s="10"/>
       <c r="K36" s="3" t="s">
@@ -11862,7 +14889,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="10"/>
       <c r="H37" s="14" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="I37" s="10"/>
       <c r="K37" s="3" t="s">
@@ -11894,13 +14921,13 @@
         <v>53</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>56</v>
@@ -11949,7 +14976,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="10"/>
       <c r="H39" s="14" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="I39" s="10"/>
       <c r="K39" s="3" t="s">
@@ -11978,7 +15005,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="10"/>
       <c r="H40" s="14" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="I40" s="10"/>
       <c r="K40" s="3" t="s">
@@ -12007,7 +15034,7 @@
       <c r="D41" s="3"/>
       <c r="E41" s="10"/>
       <c r="H41" s="14" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="I41" s="10"/>
       <c r="K41" s="3" t="s">
@@ -12036,7 +15063,7 @@
       <c r="D42" s="3"/>
       <c r="E42" s="10"/>
       <c r="H42" s="14" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="I42" s="10"/>
       <c r="K42" s="3" t="s">
@@ -12065,7 +15092,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="10"/>
       <c r="H43" s="14" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="I43" s="10"/>
       <c r="K43" s="3" t="s">
@@ -12097,13 +15124,13 @@
         <v>25</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>29</v>
@@ -12152,7 +15179,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="10"/>
       <c r="H45" s="14" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="I45" s="10"/>
       <c r="K45" s="3" t="s">
@@ -12181,7 +15208,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="10"/>
       <c r="H46" s="14" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="I46" s="10"/>
       <c r="K46" s="3" t="s">
@@ -12210,7 +15237,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="10"/>
       <c r="H47" s="14" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="I47" s="10"/>
       <c r="K47" s="3" t="s">
@@ -12239,7 +15266,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="10"/>
       <c r="H48" s="14" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="I48" s="10"/>
       <c r="K48" s="3" t="s">
@@ -12268,7 +15295,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
       <c r="H49" s="14" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="I49" s="10"/>
       <c r="K49" s="3" t="s">
@@ -12297,7 +15324,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="10"/>
       <c r="H50" s="14" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="I50" s="10"/>
       <c r="K50" s="3" t="s">
@@ -12326,7 +15353,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="10"/>
       <c r="H51" s="14" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="I51" s="10"/>
       <c r="K51" s="3" t="s">
@@ -12358,13 +15385,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>56</v>
@@ -12413,7 +15440,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="10"/>
       <c r="H53" s="14" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="I53" s="10"/>
       <c r="K53" s="3" t="s">
@@ -12442,7 +15469,7 @@
       <c r="D54" s="3"/>
       <c r="E54" s="10"/>
       <c r="H54" s="14" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="I54" s="10"/>
       <c r="K54" s="3" t="s">
@@ -12471,7 +15498,7 @@
       <c r="D55" s="3"/>
       <c r="E55" s="10"/>
       <c r="H55" s="14" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="I55" s="10"/>
       <c r="K55" s="3" t="s">
@@ -12500,7 +15527,7 @@
       <c r="D56" s="3"/>
       <c r="E56" s="10"/>
       <c r="H56" s="14" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="I56" s="10"/>
       <c r="K56" s="3" t="s">
@@ -12529,7 +15556,7 @@
       <c r="D57" s="3"/>
       <c r="E57" s="11"/>
       <c r="H57" s="14" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="I57" s="10"/>
       <c r="K57" s="3" t="s">
@@ -12561,13 +15588,13 @@
         <v>25</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>29</v>
@@ -12616,7 +15643,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="10"/>
       <c r="H59" s="14" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="I59" s="10"/>
       <c r="K59" s="3" t="s">
@@ -12645,7 +15672,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="10"/>
       <c r="H60" s="14" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="I60" s="10"/>
       <c r="K60" s="3" t="s">
@@ -12674,7 +15701,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="10"/>
       <c r="H61" s="14" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="I61" s="10"/>
       <c r="K61" s="3" t="s">
@@ -12703,7 +15730,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="10"/>
       <c r="H62" s="14" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="I62" s="10"/>
       <c r="K62" s="3" t="s">
@@ -12732,7 +15759,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
       <c r="H63" s="14" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="I63" s="10"/>
       <c r="K63" s="3" t="s">
@@ -12761,7 +15788,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="10"/>
       <c r="H64" s="14" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="I64" s="10"/>
       <c r="K64" s="3" t="s">
@@ -12790,7 +15817,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="10"/>
       <c r="H65" s="14" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="I65" s="10"/>
       <c r="K65" s="3" t="s">
@@ -12822,13 +15849,13 @@
         <v>53</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>56</v>
@@ -12877,7 +15904,7 @@
       <c r="D67" s="3"/>
       <c r="E67" s="10"/>
       <c r="H67" s="14" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="I67" s="10"/>
       <c r="K67" s="3" t="s">
@@ -12906,7 +15933,7 @@
       <c r="D68" s="3"/>
       <c r="E68" s="10"/>
       <c r="H68" s="14" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="I68" s="10"/>
       <c r="K68" s="3" t="s">
@@ -12935,7 +15962,7 @@
       <c r="D69" s="3"/>
       <c r="E69" s="10"/>
       <c r="H69" s="14" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="I69" s="10"/>
       <c r="K69" s="3" t="s">
@@ -12964,7 +15991,7 @@
       <c r="D70" s="3"/>
       <c r="E70" s="10"/>
       <c r="H70" s="14" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="I70" s="10"/>
       <c r="K70" s="3" t="s">
@@ -12993,7 +16020,7 @@
       <c r="D71" s="3"/>
       <c r="E71" s="11"/>
       <c r="H71" s="14" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="I71" s="10"/>
       <c r="K71" s="3" t="s">
@@ -13017,7 +16044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W57"/>
@@ -13130,13 +16157,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -13185,7 +16212,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="10"/>
       <c r="H3" s="14" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -13214,7 +16241,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="10"/>
       <c r="H4" s="14" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -13243,7 +16270,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="10"/>
       <c r="H5" s="14" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -13272,7 +16299,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="10"/>
       <c r="H6" s="14" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -13301,7 +16328,7 @@
       <c r="D7" s="5"/>
       <c r="E7" s="11"/>
       <c r="H7" s="14" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -13330,7 +16357,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="14" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -13359,7 +16386,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="14" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -13391,13 +16418,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -13446,7 +16473,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="14" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -13475,7 +16502,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="14" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -13504,7 +16531,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="14" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -13533,7 +16560,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="14" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -13562,7 +16589,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="14" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -13594,13 +16621,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -13649,7 +16676,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="14" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -13678,7 +16705,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="14" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -13707,7 +16734,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="14" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -13736,7 +16763,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="14" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -13765,7 +16792,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="14" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -13794,7 +16821,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="14" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -13823,7 +16850,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="14" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -13855,13 +16882,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -13910,7 +16937,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="14" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -13939,7 +16966,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="14" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -13968,7 +16995,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="14" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -13997,7 +17024,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="14" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -14026,7 +17053,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="14" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -14058,13 +17085,13 @@
         <v>25</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>29</v>
@@ -14113,7 +17140,7 @@
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
       <c r="H31" s="14" t="s">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="I31" s="10"/>
       <c r="K31" s="3" t="s">
@@ -14142,7 +17169,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="10"/>
       <c r="H32" s="14" t="s">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="I32" s="10"/>
       <c r="K32" s="3" t="s">
@@ -14171,7 +17198,7 @@
       <c r="D33" s="5"/>
       <c r="E33" s="10"/>
       <c r="H33" s="14" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="I33" s="10"/>
       <c r="K33" s="3" t="s">
@@ -14200,7 +17227,7 @@
       <c r="D34" s="5"/>
       <c r="E34" s="10"/>
       <c r="H34" s="14" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="I34" s="10"/>
       <c r="K34" s="3" t="s">
@@ -14229,7 +17256,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="11"/>
       <c r="H35" s="14" t="s">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="I35" s="10"/>
       <c r="K35" s="3" t="s">
@@ -14258,7 +17285,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="10"/>
       <c r="H36" s="14" t="s">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="I36" s="10"/>
       <c r="K36" s="3" t="s">
@@ -14287,7 +17314,7 @@
       <c r="D37" s="5"/>
       <c r="E37" s="10"/>
       <c r="H37" s="14" t="s">
-        <v>223</v>
+        <v>291</v>
       </c>
       <c r="I37" s="10"/>
       <c r="K37" s="3" t="s">
@@ -14319,13 +17346,13 @@
         <v>53</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>56</v>
@@ -14374,7 +17401,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="10"/>
       <c r="H39" s="14" t="s">
-        <v>226</v>
+        <v>294</v>
       </c>
       <c r="I39" s="10"/>
       <c r="K39" s="3" t="s">
@@ -14403,7 +17430,7 @@
       <c r="D40" s="3"/>
       <c r="E40" s="10"/>
       <c r="H40" s="14" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="I40" s="10"/>
       <c r="K40" s="3" t="s">
@@ -14432,7 +17459,7 @@
       <c r="D41" s="3"/>
       <c r="E41" s="10"/>
       <c r="H41" s="14" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
       <c r="I41" s="10"/>
       <c r="K41" s="3" t="s">
@@ -14461,7 +17488,7 @@
       <c r="D42" s="3"/>
       <c r="E42" s="10"/>
       <c r="H42" s="14" t="s">
-        <v>229</v>
+        <v>297</v>
       </c>
       <c r="I42" s="10"/>
       <c r="K42" s="3" t="s">
@@ -14490,7 +17517,7 @@
       <c r="D43" s="3"/>
       <c r="E43" s="10"/>
       <c r="H43" s="14" t="s">
-        <v>230</v>
+        <v>298</v>
       </c>
       <c r="I43" s="10"/>
       <c r="K43" s="3" t="s">
@@ -14522,13 +17549,13 @@
         <v>25</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>29</v>
@@ -14577,7 +17604,7 @@
       <c r="D45" s="5"/>
       <c r="E45" s="10"/>
       <c r="H45" s="14" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
       <c r="I45" s="10"/>
       <c r="K45" s="3" t="s">
@@ -14606,7 +17633,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="10"/>
       <c r="H46" s="14" t="s">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="I46" s="10"/>
       <c r="K46" s="3" t="s">
@@ -14635,7 +17662,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="10"/>
       <c r="H47" s="14" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="I47" s="10"/>
       <c r="K47" s="3" t="s">
@@ -14664,7 +17691,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="10"/>
       <c r="H48" s="14" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="I48" s="10"/>
       <c r="K48" s="3" t="s">
@@ -14693,7 +17720,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
       <c r="H49" s="14" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="I49" s="10"/>
       <c r="K49" s="3" t="s">
@@ -14722,7 +17749,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="10"/>
       <c r="H50" s="14" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="I50" s="10"/>
       <c r="K50" s="3" t="s">
@@ -14751,7 +17778,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="10"/>
       <c r="H51" s="14" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="I51" s="10"/>
       <c r="K51" s="3" t="s">
@@ -14783,13 +17810,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>56</v>
@@ -14838,7 +17865,7 @@
       <c r="D53" s="3"/>
       <c r="E53" s="10"/>
       <c r="H53" s="14" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="I53" s="10"/>
       <c r="K53" s="3" t="s">
@@ -14867,7 +17894,7 @@
       <c r="D54" s="3"/>
       <c r="E54" s="10"/>
       <c r="H54" s="14" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="I54" s="10"/>
       <c r="K54" s="3" t="s">
@@ -14896,7 +17923,7 @@
       <c r="D55" s="3"/>
       <c r="E55" s="10"/>
       <c r="H55" s="14" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="I55" s="10"/>
       <c r="K55" s="3" t="s">
@@ -14925,7 +17952,7 @@
       <c r="D56" s="3"/>
       <c r="E56" s="10"/>
       <c r="H56" s="14" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="I56" s="10"/>
       <c r="K56" s="3" t="s">
@@ -14954,7 +17981,7 @@
       <c r="D57" s="3"/>
       <c r="E57" s="10"/>
       <c r="H57" s="14" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="I57" s="10"/>
       <c r="K57" s="3" t="s">
@@ -14978,7 +18005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W29"/>
@@ -15091,13 +18118,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>29</v>
@@ -15146,7 +18173,7 @@
       <c r="D3" s="5"/>
       <c r="E3" s="10"/>
       <c r="H3" s="14" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="I3" s="10"/>
       <c r="K3" s="3" t="s">
@@ -15175,7 +18202,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="10"/>
       <c r="H4" s="14" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="I4" s="10"/>
       <c r="K4" s="3" t="s">
@@ -15204,7 +18231,7 @@
       <c r="D5" s="5"/>
       <c r="E5" s="10"/>
       <c r="H5" s="14" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="I5" s="10"/>
       <c r="K5" s="3" t="s">
@@ -15233,7 +18260,7 @@
       <c r="D6" s="5"/>
       <c r="E6" s="10"/>
       <c r="H6" s="14" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="I6" s="10"/>
       <c r="K6" s="3" t="s">
@@ -15262,7 +18289,7 @@
       <c r="D7" s="5"/>
       <c r="E7" s="11"/>
       <c r="H7" s="14" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="I7" s="10"/>
       <c r="K7" s="3" t="s">
@@ -15291,7 +18318,7 @@
       <c r="D8" s="5"/>
       <c r="E8" s="10"/>
       <c r="H8" s="14" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="I8" s="10"/>
       <c r="K8" s="3" t="s">
@@ -15320,7 +18347,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="10"/>
       <c r="H9" s="14" t="s">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="I9" s="10"/>
       <c r="K9" s="3" t="s">
@@ -15352,13 +18379,13 @@
         <v>53</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>56</v>
@@ -15407,7 +18434,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
       <c r="H11" s="14" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="I11" s="10"/>
       <c r="K11" s="3" t="s">
@@ -15436,7 +18463,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="10"/>
       <c r="H12" s="14" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="I12" s="10"/>
       <c r="K12" s="3" t="s">
@@ -15465,7 +18492,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
       <c r="H13" s="14" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="I13" s="10"/>
       <c r="K13" s="3" t="s">
@@ -15494,7 +18521,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
       <c r="H14" s="14" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="I14" s="10"/>
       <c r="K14" s="3" t="s">
@@ -15523,7 +18550,7 @@
       <c r="D15" s="3"/>
       <c r="E15" s="11"/>
       <c r="H15" s="14" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="I15" s="10"/>
       <c r="K15" s="3" t="s">
@@ -15555,13 +18582,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>29</v>
@@ -15610,7 +18637,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="10"/>
       <c r="H17" s="14" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="I17" s="10"/>
       <c r="K17" s="3" t="s">
@@ -15639,7 +18666,7 @@
       <c r="D18" s="5"/>
       <c r="E18" s="10"/>
       <c r="H18" s="14" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="I18" s="10"/>
       <c r="K18" s="3" t="s">
@@ -15668,7 +18695,7 @@
       <c r="D19" s="5"/>
       <c r="E19" s="10"/>
       <c r="H19" s="14" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="I19" s="10"/>
       <c r="K19" s="3" t="s">
@@ -15697,7 +18724,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="10"/>
       <c r="H20" s="14" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="I20" s="10"/>
       <c r="K20" s="3" t="s">
@@ -15726,7 +18753,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="11"/>
       <c r="H21" s="14" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="I21" s="10"/>
       <c r="K21" s="3" t="s">
@@ -15755,7 +18782,7 @@
       <c r="D22" s="5"/>
       <c r="E22" s="10"/>
       <c r="H22" s="14" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="I22" s="10"/>
       <c r="K22" s="3" t="s">
@@ -15784,7 +18811,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="10"/>
       <c r="H23" s="14" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="I23" s="10"/>
       <c r="K23" s="3" t="s">
@@ -15816,13 +18843,13 @@
         <v>53</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>56</v>
@@ -15871,7 +18898,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="10"/>
       <c r="H25" s="14" t="s">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="I25" s="10"/>
       <c r="K25" s="3" t="s">
@@ -15900,7 +18927,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="10"/>
       <c r="H26" s="14" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="I26" s="10"/>
       <c r="K26" s="3" t="s">
@@ -15929,7 +18956,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="10"/>
       <c r="H27" s="14" t="s">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="I27" s="10"/>
       <c r="K27" s="3" t="s">
@@ -15958,7 +18985,7 @@
       <c r="D28" s="3"/>
       <c r="E28" s="10"/>
       <c r="H28" s="14" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="I28" s="10"/>
       <c r="K28" s="3" t="s">
@@ -15987,7 +19014,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="11"/>
       <c r="H29" s="14" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="I29" s="10"/>
       <c r="K29" s="3" t="s">
@@ -16011,7 +19038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W57"/>
@@ -17826,573 +20853,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
-  <cols>
-    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
-    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
-    <col min="3" max="3" width="26.5" customWidth="1"/>
-    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
-    <col min="5" max="5" width="16.8303571428571" customWidth="1"/>
-    <col min="6" max="6" width="10.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="9.51785714285714" customWidth="1"/>
-    <col min="8" max="8" width="33.1875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.8303571428571" customWidth="1"/>
-    <col min="10" max="10" width="22.8303571428571" customWidth="1"/>
-    <col min="11" max="11" width="35.8303571428571" customWidth="1"/>
-    <col min="12" max="12" width="10.8303571428571" customWidth="1"/>
-    <col min="13" max="14" width="8.83035714285714" customWidth="1"/>
-    <col min="15" max="15" width="12.8303571428571" customWidth="1"/>
-    <col min="16" max="16" width="10.8303571428571" customWidth="1"/>
-    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
-    <col min="18" max="20" width="10.8303571428571" customWidth="1"/>
-    <col min="21" max="21" width="8.83035714285714" customWidth="1"/>
-    <col min="22" max="22" width="18.8303571428571" customWidth="1"/>
-    <col min="23" max="23" width="10.8303571428571" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:23">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="N2" s="3">
-        <v>500</v>
-      </c>
-      <c r="O2" s="8">
-        <v>46116</v>
-      </c>
-      <c r="P2" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:23">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="10"/>
-      <c r="H3" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="K3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="W3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:23">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="10"/>
-      <c r="H4" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="K4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="W4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:23">
-      <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="10"/>
-      <c r="H5" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="K5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="W5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:23">
-      <c r="A6" s="3">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="10"/>
-      <c r="H6" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="K6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="W6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:23">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="11"/>
-      <c r="H7" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="K7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="W7" s="3"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:23">
-      <c r="A8" s="3">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="10"/>
-      <c r="H8" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="K8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="W8" s="3"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:23">
-      <c r="A9" s="3">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="10"/>
-      <c r="H9" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="K9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="W9" s="3"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:23">
-      <c r="A10" s="3">
-        <v>2</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="N10" s="3">
-        <v>500</v>
-      </c>
-      <c r="O10" s="8">
-        <v>46116</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:23">
-      <c r="A11" s="3">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="10"/>
-      <c r="H11" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="K11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="W11" s="3"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:23">
-      <c r="A12" s="3">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="10"/>
-      <c r="H12" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="K12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="W12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:23">
-      <c r="A13" s="3">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="10"/>
-      <c r="H13" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="K13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="W13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:23">
-      <c r="A14" s="3">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="10"/>
-      <c r="H14" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="K14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="W14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:23">
-      <c r="A15" s="3">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="11"/>
-      <c r="H15" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="K15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="W15" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
+++ b/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="任务列表" sheetId="1" r:id="rId1"/>
-    <sheet name="任务列表 (4)" sheetId="5" r:id="rId2"/>
-    <sheet name="任务列表 (3)" sheetId="4" r:id="rId3"/>
-    <sheet name="任务列表 (2)" sheetId="3" r:id="rId4"/>
-    <sheet name="字段说明" sheetId="2" r:id="rId5"/>
+    <sheet name="任务列表 (5)" sheetId="6" r:id="rId2"/>
+    <sheet name="任务列表 (4)" sheetId="5" r:id="rId3"/>
+    <sheet name="任务列表 (3)" sheetId="4" r:id="rId4"/>
+    <sheet name="任务列表 (2)" sheetId="3" r:id="rId5"/>
+    <sheet name="字段说明" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="231">
   <si>
     <t>任务</t>
   </si>
@@ -120,250 +121,400 @@
     <t>IDNLow-X</t>
   </si>
   <si>
+    <t>谈种植醋-IDN</t>
+  </si>
+  <si>
+    <t>关</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>谈种植醋</t>
+  </si>
+  <si>
+    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>18+</t>
+  </si>
+  <si>
+    <t>Drama World</t>
+  </si>
+  <si>
+    <t>7561697079815438353</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
+  </si>
+  <si>
+    <t>7561696341420949511</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>7561696677241896967</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
+  </si>
+  <si>
+    <t>7571017788207300615</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
+  </si>
+  <si>
+    <t>7532007814081331208</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
+  </si>
+  <si>
+    <t>7571020884027408400</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>7532009013018525697</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-谈种植醋-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
+  </si>
+  <si>
+    <t>乔阳似火-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>乔阳似火</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-乔阳似火-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>罗飞的一天-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>罗飞的一天</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-罗飞的一天-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>落入陷阱-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>落入陷阱</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-落入陷阱-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>开单开到大动脉来-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>开单开到大动脉来</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>7560621443281731601</t>
+  </si>
+  <si>
+    <t>THA-低-C</t>
+  </si>
+  <si>
+    <t>开单开到大动脉来-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-1-S+tr</t>
+  </si>
+  <si>
+    <t>ph-1,hmj-1,MX2</t>
+  </si>
+  <si>
+    <t>7560621279238422536</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-2-S+tr</t>
+  </si>
+  <si>
+    <t>ph-2,hmj-2,MX3</t>
+  </si>
+  <si>
+    <t>7565807512133779474</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-3-S+tr</t>
+  </si>
+  <si>
+    <t>ph-3,hmj-3,wz-5</t>
+  </si>
+  <si>
+    <t>7565807154830295058</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-4-S+tr</t>
+  </si>
+  <si>
+    <t>wz1,wz2,wz3</t>
+  </si>
+  <si>
+    <t>7565807717149589521</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-5-S+tr</t>
+  </si>
+  <si>
+    <t>zyf-1,hsx-1,zzz泰国1</t>
+  </si>
+  <si>
+    <t>7565807676807036946</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-开单开到大动脉来-49T-6-S+tr</t>
+  </si>
+  <si>
+    <t>zzz泰国3,hsx-2,wz-7</t>
+  </si>
+  <si>
+    <t>我一胎十个-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>我一胎十个</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>我一胎十个-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-1-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-2-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-3-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-4-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-5-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我一胎十个-49T-6-S+tr</t>
+  </si>
+  <si>
+    <t>我能打十个-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-1</t>
+  </si>
+  <si>
+    <t>我能打十个</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-2</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-3</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-4</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-5</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-6</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-7</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-我能打十个-2.8W-S+xd-8</t>
+  </si>
+  <si>
+    <t>我能打十个-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-1-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-2-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-3-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-4-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-5-S+tr</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-我能打十个-49T-6-S+tr</t>
+  </si>
+  <si>
     <t>我来了你别慌-IDN</t>
   </si>
   <si>
-    <t>关</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-1</t>
   </si>
   <si>
     <t>我来了你别慌</t>
   </si>
   <si>
-    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
-  </si>
-  <si>
-    <t>价值</t>
-  </si>
-  <si>
-    <t>18+</t>
-  </si>
-  <si>
-    <t>Drama World</t>
-  </si>
-  <si>
-    <t>7561697079815438353</t>
+    <t>zzz印尼9</t>
   </si>
   <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-2</t>
   </si>
   <si>
-    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
-  </si>
-  <si>
-    <t>7561696341420949511</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-3</t>
   </si>
   <si>
-    <t>7561696677241896967</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-4</t>
   </si>
   <si>
-    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
-  </si>
-  <si>
-    <t>7571017788207300615</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-5</t>
   </si>
   <si>
-    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
-  </si>
-  <si>
-    <t>7532007814081331208</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-6</t>
   </si>
   <si>
-    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
-  </si>
-  <si>
-    <t>7571020884027408400</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-7</t>
   </si>
   <si>
-    <t>7532009013018525697</t>
-  </si>
-  <si>
     <t>C-xd-IDN-我来了你别慌-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
-  </si>
-  <si>
-    <t>7560621443281731601</t>
-  </si>
-  <si>
-    <t>THA-低-C</t>
-  </si>
-  <si>
-    <t>我来了你别慌-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>ph-1,hmj-1,MX2</t>
-  </si>
-  <si>
-    <t>7560621279238422536</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>ph-2,hmj-2,MX3</t>
-  </si>
-  <si>
-    <t>7565807512133779474</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>ph-3,hmj-3,wz-5</t>
-  </si>
-  <si>
-    <t>7565807154830295058</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>wz1,wz2,wz3</t>
-  </si>
-  <si>
-    <t>7565807717149589521</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>zyf-1,hsx-1,zzz泰国1</t>
-  </si>
-  <si>
-    <t>7565807676807036946</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我来了你别慌-49T-6-S+tr</t>
-  </si>
-  <si>
-    <t>zzz泰国3,hsx-2,wz-7</t>
-  </si>
-  <si>
-    <t>抓娃娃也不装了-IDN</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-1</t>
-  </si>
-  <si>
-    <t>抓娃娃也不装了</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-2</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-3</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-4</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-5</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-6</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-7</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-抓娃娃也不装了-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>抓娃娃也不装了-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-抓娃娃也不装了-49T-6-S+tr</t>
-  </si>
-  <si>
-    <t>炒房客的春天-IDN</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-1</t>
-  </si>
-  <si>
-    <t>炒房客的春天</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-2</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-3</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-4</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-5</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-6</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-7</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-炒房客的春天-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>炒房客的春天-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-炒房客的春天-49T-6-S+tr</t>
-  </si>
-  <si>
-    <t>zzz印尼9</t>
   </si>
   <si>
     <t>GF</t>
@@ -1647,6 +1798,1171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:Z33"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
+    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
+    <col min="3" max="3" width="28.5625" customWidth="1"/>
+    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="18.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="16.8303571428571" customWidth="1"/>
+    <col min="7" max="7" width="12.8303571428571" customWidth="1"/>
+    <col min="8" max="8" width="14.8303571428571" customWidth="1"/>
+    <col min="9" max="9" width="30.8303571428571" customWidth="1"/>
+    <col min="10" max="10" width="14.8303571428571" customWidth="1"/>
+    <col min="11" max="11" width="22.8303571428571" customWidth="1"/>
+    <col min="12" max="12" width="35.8303571428571" customWidth="1"/>
+    <col min="13" max="13" width="10.8303571428571" customWidth="1"/>
+    <col min="14" max="15" width="8.83035714285714" customWidth="1"/>
+    <col min="16" max="16" width="21.7232142857143" customWidth="1"/>
+    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
+    <col min="18" max="18" width="12.8303571428571" customWidth="1"/>
+    <col min="19" max="19" width="10.8303571428571" customWidth="1"/>
+    <col min="20" max="20" width="6.83035714285714" customWidth="1"/>
+    <col min="21" max="23" width="10.8303571428571" customWidth="1"/>
+    <col min="24" max="24" width="8.83035714285714" customWidth="1"/>
+    <col min="25" max="25" width="18.8303571428571" customWidth="1"/>
+    <col min="26" max="26" width="10.8303571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:26">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:26">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4"/>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4"/>
+      <c r="N4" s="2"/>
+      <c r="O4"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4" s="2"/>
+      <c r="Y4"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5"/>
+      <c r="L5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5"/>
+      <c r="N5" s="2"/>
+      <c r="O5"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5" s="2"/>
+      <c r="Y5"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="I6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="L6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6"/>
+      <c r="N6" s="2"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="I7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="L7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7"/>
+      <c r="N7" s="2"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="I8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="L8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8"/>
+      <c r="N8" s="2"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="I9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="L9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9"/>
+      <c r="N9" s="2"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:26">
+      <c r="A10" s="2">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:26">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="G11"/>
+      <c r="I11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="L11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:26">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="I12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="L12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:26">
+      <c r="A13" s="2">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="I13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="L13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:26">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="I14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="L14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:26">
+      <c r="A15" s="2">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="I15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="L15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:26">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="I16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="L16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:26">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="I17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="L17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Z17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:26">
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" t="s">
+        <v>34</v>
+      </c>
+      <c r="N18" s="2">
+        <v>2</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>1</v>
+      </c>
+      <c r="R18" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:26">
+      <c r="A19" s="2">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="G19"/>
+      <c r="I19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="L19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19"/>
+      <c r="Z19" s="2"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:26">
+      <c r="A20" s="2">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="I20" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="L20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Z20" s="2"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:26">
+      <c r="A21" s="2">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="I21" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="L21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Z21" s="2"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:26">
+      <c r="A22" s="2">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="I22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="L22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Z22" s="2"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:26">
+      <c r="A23" s="2">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="I23" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="L23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Z23" s="2"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:26">
+      <c r="A24" s="2">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="I24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="L24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Z24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:26">
+      <c r="A25" s="2">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="I25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="L25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Z25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:26">
+      <c r="A26" s="2">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="2">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>1</v>
+      </c>
+      <c r="R26" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S26" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:26">
+      <c r="A27" s="2">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="G27"/>
+      <c r="I27" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="5"/>
+      <c r="L27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:26">
+      <c r="A28" s="2">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="I28" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="5"/>
+      <c r="L28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Z28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:26">
+      <c r="A29" s="2">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="I29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="L29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Z29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:26">
+      <c r="A30" s="2">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="I30" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="L30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Z30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:26">
+      <c r="A31" s="2">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="I31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J31" s="5"/>
+      <c r="L31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Z31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:26">
+      <c r="A32" s="2">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="I32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="J32" s="5"/>
+      <c r="L32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Z32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:26">
+      <c r="A33" s="2">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="I33" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="L33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Z33" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Z1" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Z43"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
@@ -1768,19 +3084,19 @@
       <c r="D2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>29</v>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>88</v>
+      </c>
       <c r="L2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1792,16 +3108,16 @@
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="Q2" s="1">
         <v>1</v>
       </c>
       <c r="R2" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S2" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>35</v>
@@ -1830,23 +3146,17 @@
         <v>37</v>
       </c>
       <c r="D3" s="10"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="8"/>
       <c r="G3"/>
-      <c r="H3" s="1"/>
       <c r="I3" s="9" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="J3" s="5"/>
-      <c r="K3" s="1"/>
       <c r="L3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M3"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
       <c r="R3" s="6"/>
       <c r="S3" s="7"/>
       <c r="T3" s="2"/>
@@ -1866,31 +3176,21 @@
         <v>40</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4"/>
-      <c r="F4" s="8"/>
-      <c r="G4"/>
-      <c r="H4"/>
       <c r="I4" s="9" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="J4" s="5"/>
-      <c r="K4"/>
       <c r="L4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M4"/>
       <c r="N4" s="2"/>
-      <c r="O4"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="6"/>
       <c r="S4" s="7"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4"/>
-      <c r="W4"/>
       <c r="X4" s="2"/>
-      <c r="Y4"/>
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26">
@@ -1902,31 +3202,21 @@
         <v>42</v>
       </c>
       <c r="D5" s="10"/>
-      <c r="E5"/>
-      <c r="F5" s="8"/>
-      <c r="G5"/>
-      <c r="H5"/>
       <c r="I5" s="9" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5"/>
       <c r="L5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M5"/>
       <c r="N5" s="2"/>
-      <c r="O5"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="6"/>
       <c r="S5" s="7"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5"/>
-      <c r="W5"/>
       <c r="X5" s="2"/>
-      <c r="Y5"/>
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26">
@@ -1938,16 +3228,13 @@
         <v>45</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="F6" s="8"/>
-      <c r="G6"/>
       <c r="I6" s="9" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="J6" s="5"/>
       <c r="L6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M6"/>
       <c r="N6" s="2"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1956,7 +3243,6 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6"/>
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26">
@@ -1968,16 +3254,13 @@
         <v>48</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="F7" s="8"/>
-      <c r="G7"/>
       <c r="I7" s="9" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="J7" s="5"/>
       <c r="L7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M7"/>
       <c r="N7" s="2"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1986,7 +3269,6 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7"/>
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26">
@@ -1998,16 +3280,13 @@
         <v>51</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="F8" s="8"/>
-      <c r="G8"/>
       <c r="I8" s="9" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="J8" s="5"/>
       <c r="L8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M8"/>
       <c r="N8" s="2"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -2016,7 +3295,6 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8"/>
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26">
@@ -2028,16 +3306,13 @@
         <v>53</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="F9" s="8"/>
-      <c r="G9"/>
       <c r="I9" s="9" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="J9" s="5"/>
       <c r="L9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M9"/>
       <c r="N9" s="2"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -2046,7 +3321,6 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9"/>
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26">
@@ -2057,25 +3331,26 @@
         <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>58</v>
+        <v>97</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>59</v>
+      <c r="I10" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
         <v>34</v>
@@ -2085,16 +3360,16 @@
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
       </c>
       <c r="R10" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S10" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>35</v>
@@ -2120,19 +3395,16 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="F11" s="8"/>
-      <c r="G11"/>
-      <c r="I11" s="4" t="s">
-        <v>62</v>
+      <c r="I11" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="J11" s="5"/>
       <c r="L11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M11"/>
+        <v>103</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -2141,7 +3413,6 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11"/>
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26">
@@ -2149,13 +3420,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>65</v>
+        <v>104</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -2163,13 +3434,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -2177,13 +3448,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>71</v>
+        <v>110</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -2191,13 +3462,13 @@
         <v>2</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>74</v>
+        <v>113</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:26">
@@ -2213,17 +3484,18 @@
       <c r="D16" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>33</v>
@@ -2236,16 +3508,16 @@
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="Q16" s="1">
         <v>1</v>
       </c>
       <c r="R16" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S16" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>35</v>
@@ -2274,10 +3546,9 @@
         <v>37</v>
       </c>
       <c r="D17" s="10"/>
-      <c r="F17" s="8"/>
       <c r="G17"/>
       <c r="I17" s="9" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="J17" s="5"/>
       <c r="L17" s="2" t="s">
@@ -2305,9 +3576,8 @@
         <v>40</v>
       </c>
       <c r="D18" s="10"/>
-      <c r="F18" s="8"/>
       <c r="I18" s="9" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J18" s="5"/>
       <c r="L18" s="2" t="s">
@@ -2332,9 +3602,8 @@
         <v>42</v>
       </c>
       <c r="D19" s="10"/>
-      <c r="F19" s="8"/>
       <c r="I19" s="9" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="J19" s="5"/>
       <c r="L19" s="2" t="s">
@@ -2359,9 +3628,8 @@
         <v>45</v>
       </c>
       <c r="D20" s="10"/>
-      <c r="F20" s="8"/>
       <c r="I20" s="9" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="J20" s="5"/>
       <c r="L20" s="2" t="s">
@@ -2386,9 +3654,8 @@
         <v>48</v>
       </c>
       <c r="D21" s="10"/>
-      <c r="F21" s="8"/>
       <c r="I21" s="9" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="J21" s="5"/>
       <c r="L21" s="2" t="s">
@@ -2413,9 +3680,8 @@
         <v>51</v>
       </c>
       <c r="D22" s="10"/>
-      <c r="F22" s="8"/>
       <c r="I22" s="9" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="J22" s="5"/>
       <c r="L22" s="2" t="s">
@@ -2440,9 +3706,8 @@
         <v>53</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="F23" s="8"/>
       <c r="I23" s="9" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="J23" s="5"/>
       <c r="L23" s="2" t="s">
@@ -2466,25 +3731,26 @@
         <v>26</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="G24" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s">
         <v>34</v>
@@ -2494,16 +3760,16 @@
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Q24" s="1">
         <v>1</v>
       </c>
       <c r="R24" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S24" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>35</v>
@@ -2529,16 +3795,15 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="4" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D25" s="10"/>
-      <c r="F25" s="8"/>
       <c r="I25" s="9" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="J25" s="5"/>
       <c r="L25" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="N25" s="2"/>
       <c r="P25" s="1"/>
@@ -2555,13 +3820,13 @@
         <v>4</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:26">
@@ -2569,13 +3834,13 @@
         <v>4</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:26">
@@ -2583,13 +3848,13 @@
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:26">
@@ -2597,13 +3862,13 @@
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:26">
@@ -2619,17 +3884,18 @@
       <c r="D30" s="10" t="s">
         <v>28</v>
       </c>
+      <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="G30" t="s">
         <v>30</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>33</v>
@@ -2642,16 +3908,16 @@
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="Q30" s="1">
         <v>1</v>
       </c>
       <c r="R30" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S30" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>35</v>
@@ -2680,10 +3946,9 @@
         <v>37</v>
       </c>
       <c r="D31" s="10"/>
-      <c r="F31" s="8"/>
       <c r="G31"/>
       <c r="I31" s="9" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="J31" s="5"/>
       <c r="L31" s="2" t="s">
@@ -2711,9 +3976,8 @@
         <v>40</v>
       </c>
       <c r="D32" s="10"/>
-      <c r="F32" s="8"/>
       <c r="I32" s="9" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="J32" s="5"/>
       <c r="L32" s="2" t="s">
@@ -2738,9 +4002,8 @@
         <v>42</v>
       </c>
       <c r="D33" s="10"/>
-      <c r="F33" s="8"/>
       <c r="I33" s="9" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="J33" s="5"/>
       <c r="L33" s="2" t="s">
@@ -2765,9 +4028,8 @@
         <v>45</v>
       </c>
       <c r="D34" s="10"/>
-      <c r="F34" s="8"/>
       <c r="I34" s="9" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="J34" s="5"/>
       <c r="L34" s="2" t="s">
@@ -2792,9 +4054,8 @@
         <v>48</v>
       </c>
       <c r="D35" s="10"/>
-      <c r="F35" s="8"/>
       <c r="I35" s="9" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J35" s="5"/>
       <c r="L35" s="2" t="s">
@@ -2819,9 +4080,8 @@
         <v>51</v>
       </c>
       <c r="D36" s="10"/>
-      <c r="F36" s="8"/>
       <c r="I36" s="9" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="J36" s="5"/>
       <c r="L36" s="2" t="s">
@@ -2846,9 +4106,8 @@
         <v>53</v>
       </c>
       <c r="D37" s="10"/>
-      <c r="F37" s="8"/>
       <c r="I37" s="9" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="J37" s="5"/>
       <c r="L37" s="2" t="s">
@@ -2872,25 +4131,26 @@
         <v>26</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="G38" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M38" t="s">
         <v>34</v>
@@ -2900,16 +4160,16 @@
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Q38" s="1">
         <v>1</v>
       </c>
       <c r="R38" s="6">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="S38" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>35</v>
@@ -2935,16 +4195,15 @@
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="4" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D39" s="10"/>
-      <c r="F39" s="8"/>
       <c r="I39" s="9" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="J39" s="5"/>
       <c r="L39" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="N39" s="2"/>
       <c r="P39" s="1"/>
@@ -2961,13 +4220,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="I40" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:26">
@@ -2975,13 +4234,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:26">
@@ -2989,13 +4248,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:26">
@@ -3003,25 +4262,22 @@
         <v>6</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:Z1" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z11"/>
@@ -3146,19 +4402,19 @@
         <v>28</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M2" t="s">
         <v>34</v>
@@ -3211,19 +4467,19 @@
         <v>28</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
@@ -3276,19 +4532,19 @@
         <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M4" t="s">
         <v>34</v>
@@ -3338,19 +4594,19 @@
         <v>28</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s">
         <v>34</v>
@@ -3400,19 +4656,19 @@
         <v>28</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
@@ -3462,19 +4718,19 @@
         <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
@@ -3524,19 +4780,19 @@
         <v>28</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M8" t="s">
         <v>34</v>
@@ -3586,19 +4842,19 @@
         <v>28</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M9" t="s">
         <v>34</v>
@@ -3678,7 +4934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z9"/>
@@ -3794,28 +5050,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M2" t="s">
         <v>34</v>
@@ -3859,28 +5115,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
@@ -3924,28 +5180,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M4" t="s">
         <v>34</v>
@@ -3986,28 +5242,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s">
         <v>34</v>
@@ -4048,28 +5304,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
@@ -4110,28 +5366,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
@@ -4172,28 +5428,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M8" t="s">
         <v>34</v>
@@ -4234,28 +5490,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="M9" t="s">
         <v>34</v>
@@ -4297,7 +5553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z3"/>
@@ -4413,25 +5669,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>33</v>
@@ -4477,25 +5733,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
@@ -4543,7 +5799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D27"/>
@@ -4557,16 +5813,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="B1" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="D1" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4574,13 +5830,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4588,10 +5844,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -4602,10 +5858,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -4616,10 +5872,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -4630,13 +5886,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4644,13 +5900,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4658,10 +5914,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -4672,13 +5928,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4686,13 +5942,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4700,13 +5956,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4714,13 +5970,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4728,13 +5984,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4742,10 +5998,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
@@ -4756,13 +6012,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4770,13 +6026,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4784,13 +6040,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4798,13 +6054,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4812,13 +6068,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4826,13 +6082,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4840,10 +6096,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
@@ -4854,13 +6110,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4868,13 +6124,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4882,13 +6138,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4896,13 +6152,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D25" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4910,10 +6166,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
         <v>30</v>
@@ -4924,13 +6180,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="D27" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
+++ b/管理系统批量脚本工具/ad-automation3.0/data/tasks-v3.0.xlsx
@@ -4,15 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="14760"/>
+    <workbookView windowHeight="14780" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="任务列表" sheetId="1" r:id="rId1"/>
-    <sheet name="任务列表 (5)" sheetId="6" r:id="rId2"/>
-    <sheet name="任务列表 (4)" sheetId="5" r:id="rId3"/>
-    <sheet name="任务列表 (3)" sheetId="4" r:id="rId4"/>
-    <sheet name="任务列表 (2)" sheetId="3" r:id="rId5"/>
-    <sheet name="字段说明" sheetId="2" r:id="rId6"/>
+    <sheet name="价值广告 (商品) (2)" sheetId="8" r:id="rId1"/>
+    <sheet name="价值广告 (商品)" sheetId="7" r:id="rId2"/>
+    <sheet name="价值广告" sheetId="6" r:id="rId3"/>
+    <sheet name="下单广告" sheetId="1" r:id="rId4"/>
+    <sheet name="任务列表 (4)" sheetId="5" r:id="rId5"/>
+    <sheet name="任务列表 (3)" sheetId="4" r:id="rId6"/>
+    <sheet name="任务列表 (2)" sheetId="3" r:id="rId7"/>
+    <sheet name="字段说明" sheetId="2" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="211">
   <si>
     <t>任务</t>
   </si>
@@ -115,93 +117,225 @@
     <t>MAD</t>
   </si>
   <si>
+    <t>7561696495247278087</t>
+  </si>
+  <si>
+    <t>IDNLow-X</t>
+  </si>
+  <si>
+    <t>邙山印记-IDN</t>
+  </si>
+  <si>
+    <t>开</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-邙山印记-2.8W-S+xd-9-商</t>
+  </si>
+  <si>
+    <t>邙山印记</t>
+  </si>
+  <si>
+    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>18+</t>
+  </si>
+  <si>
+    <t>Drama World</t>
+  </si>
+  <si>
+    <t>C-商品库</t>
+  </si>
+  <si>
+    <t>IDN-TaDEFaZe</t>
+  </si>
+  <si>
+    <t>关</t>
+  </si>
+  <si>
+    <t>7561696693796995073</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-邙山印记-2.8W-S+xd-10-商</t>
+  </si>
+  <si>
+    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
+  </si>
+  <si>
+    <t>7565807915412897810</t>
+  </si>
+  <si>
+    <t>THA-低-C</t>
+  </si>
+  <si>
+    <t>邙山印记-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-邙山印记-49T-7-S+tr-商</t>
+  </si>
+  <si>
+    <t>ph-1,hmj-1,MX2</t>
+  </si>
+  <si>
+    <t>Thai-TaDEFaZe</t>
+  </si>
+  <si>
+    <t>7565807719937064968</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-邙山印记-49T-8-S+tr-商</t>
+  </si>
+  <si>
+    <t>ph-2,hmj-2,MX3</t>
+  </si>
+  <si>
+    <t>白日枫林晚-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-白日枫林晚-2.8W-S+xd-9-商</t>
+  </si>
+  <si>
+    <t>白日枫林晚</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-白日枫林晚-2.8W-S+xd-10-商</t>
+  </si>
+  <si>
+    <t>7595503602177671184</t>
+  </si>
+  <si>
+    <t>白日枫林晚-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-白日枫林晚-49T-9-S+tr-商</t>
+  </si>
+  <si>
+    <t>7595502829645807634</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-白日枫林晚-49T-10-S+tr-商</t>
+  </si>
+  <si>
+    <t>黄河入海流-IDN</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-黄河入海流-2.8W-S+xd-9-商</t>
+  </si>
+  <si>
+    <t>黄河入海流</t>
+  </si>
+  <si>
+    <t>C-xd-IDN-黄河入海流-2.8W-S+xd-10-商</t>
+  </si>
+  <si>
+    <t>黄河入海流-THAI</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-黄河入海流-49T-9-S+tr-商</t>
+  </si>
+  <si>
+    <t>C-MADxd-燥米-黄河入海流-49T-10-S+tr-商</t>
+  </si>
+  <si>
     <t>7530554431298273297</t>
   </si>
   <si>
-    <t>IDNLow-X</t>
+    <t>7561697079815438353</t>
+  </si>
+  <si>
+    <t>7561696341420949511</t>
+  </si>
+  <si>
+    <t>7561696677241896967</t>
+  </si>
+  <si>
+    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
+  </si>
+  <si>
+    <t>7571017788207300615</t>
+  </si>
+  <si>
+    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
+  </si>
+  <si>
+    <t>7532007814081331208</t>
+  </si>
+  <si>
+    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
+  </si>
+  <si>
+    <t>7571020884027408400</t>
+  </si>
+  <si>
+    <t>7532009013018525697</t>
+  </si>
+  <si>
+    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
+  </si>
+  <si>
+    <t>7560621443281731601</t>
+  </si>
+  <si>
+    <t>7560621279238422536</t>
+  </si>
+  <si>
+    <t>7565807512133779474</t>
+  </si>
+  <si>
+    <t>ph-3,hmj-3,wz-5</t>
+  </si>
+  <si>
+    <t>7565807154830295058</t>
+  </si>
+  <si>
+    <t>wz1,wz2,wz3</t>
+  </si>
+  <si>
+    <t>7565807717149589521</t>
+  </si>
+  <si>
+    <t>zyf-1,hsx-1,zzz泰国1</t>
+  </si>
+  <si>
+    <t>7565807676807036946</t>
+  </si>
+  <si>
+    <t>zzz泰国3,hsx-2,wz-7</t>
   </si>
   <si>
     <t>谈种植醋-IDN</t>
   </si>
   <si>
-    <t>关</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-1</t>
   </si>
   <si>
     <t>谈种植醋</t>
   </si>
   <si>
-    <t>zzz印尼9,hsx-印尼-7,ph-idn-5</t>
-  </si>
-  <si>
-    <t>价值</t>
-  </si>
-  <si>
-    <t>18+</t>
-  </si>
-  <si>
-    <t>Drama World</t>
-  </si>
-  <si>
-    <t>7561697079815438353</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-2</t>
   </si>
   <si>
-    <t>ph-idn-6,wz-idn-105,ph-idn-2</t>
-  </si>
-  <si>
-    <t>7561696341420949511</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-3</t>
   </si>
   <si>
-    <t>7561696677241896967</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-4</t>
   </si>
   <si>
-    <t>IDN-hmj-2,hsx-印尼-3,hsx-印尼-5</t>
-  </si>
-  <si>
-    <t>7571017788207300615</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-5</t>
   </si>
   <si>
-    <t>wz-idn-3,xd-IDN-829-2,IDN-hmj-5</t>
-  </si>
-  <si>
-    <t>7532007814081331208</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-6</t>
   </si>
   <si>
-    <t>wz-idn-104,xd-IDN-829-1,xd-IDN-829-9</t>
-  </si>
-  <si>
-    <t>7571020884027408400</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-7</t>
   </si>
   <si>
-    <t>7532009013018525697</t>
-  </si>
-  <si>
     <t>C-xd-IDN-谈种植醋-2.8W-S+xd-8</t>
   </si>
   <si>
-    <t>wz-idn-102,IDN-zyf-1,xd-IDN-829-4</t>
-  </si>
-  <si>
     <t>乔阳似火-IDN</t>
   </si>
   <si>
@@ -290,198 +424,6 @@
   </si>
   <si>
     <t>C-xd-IDN-落入陷阱-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>开单开到大动脉来-IDN</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-1</t>
-  </si>
-  <si>
-    <t>开单开到大动脉来</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-2</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-3</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-4</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-5</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-6</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-7</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-开单开到大动脉来-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>7560621443281731601</t>
-  </si>
-  <si>
-    <t>THA-低-C</t>
-  </si>
-  <si>
-    <t>开单开到大动脉来-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>ph-1,hmj-1,MX2</t>
-  </si>
-  <si>
-    <t>7560621279238422536</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>ph-2,hmj-2,MX3</t>
-  </si>
-  <si>
-    <t>7565807512133779474</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>ph-3,hmj-3,wz-5</t>
-  </si>
-  <si>
-    <t>7565807154830295058</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>wz1,wz2,wz3</t>
-  </si>
-  <si>
-    <t>7565807717149589521</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>zyf-1,hsx-1,zzz泰国1</t>
-  </si>
-  <si>
-    <t>7565807676807036946</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-开单开到大动脉来-49T-6-S+tr</t>
-  </si>
-  <si>
-    <t>zzz泰国3,hsx-2,wz-7</t>
-  </si>
-  <si>
-    <t>我一胎十个-IDN</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-1</t>
-  </si>
-  <si>
-    <t>我一胎十个</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-2</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-3</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-4</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-5</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-6</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-7</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我一胎十个-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>我一胎十个-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我一胎十个-49T-6-S+tr</t>
-  </si>
-  <si>
-    <t>我能打十个-IDN</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-1</t>
-  </si>
-  <si>
-    <t>我能打十个</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-2</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-3</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-4</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-5</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-6</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-7</t>
-  </si>
-  <si>
-    <t>C-xd-IDN-我能打十个-2.8W-S+xd-8</t>
-  </si>
-  <si>
-    <t>我能打十个-THAI</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-1-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-2-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-3-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-4-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-5-S+tr</t>
-  </si>
-  <si>
-    <t>C-MADxd-燥米-我能打十个-49T-6-S+tr</t>
   </si>
   <si>
     <t>我来了你别慌-IDN</t>
@@ -738,14 +680,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="26">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -762,12 +697,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1248,19 +1177,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1269,152 +1207,148 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1798,31 +1732,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
+    <col min="1" max="1" width="4.75892857142857" customWidth="1"/>
     <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
     <col min="3" max="3" width="28.5625" customWidth="1"/>
     <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
-    <col min="5" max="5" width="18.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="9.36607142857143" customWidth="1"/>
     <col min="6" max="6" width="16.8303571428571" customWidth="1"/>
     <col min="7" max="7" width="12.8303571428571" customWidth="1"/>
-    <col min="8" max="8" width="14.8303571428571" customWidth="1"/>
-    <col min="9" max="9" width="30.8303571428571" customWidth="1"/>
+    <col min="8" max="8" width="10.1071428571429" customWidth="1"/>
+    <col min="9" max="9" width="38.6785714285714" customWidth="1"/>
     <col min="10" max="10" width="14.8303571428571" customWidth="1"/>
-    <col min="11" max="11" width="22.8303571428571" customWidth="1"/>
-    <col min="12" max="12" width="35.8303571428571" customWidth="1"/>
-    <col min="13" max="13" width="10.8303571428571" customWidth="1"/>
-    <col min="14" max="15" width="8.83035714285714" customWidth="1"/>
-    <col min="16" max="16" width="21.7232142857143" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
+    <col min="12" max="12" width="27.2321428571429" customWidth="1"/>
+    <col min="13" max="13" width="9.07142857142857" customWidth="1"/>
+    <col min="14" max="14" width="5.20535714285714" customWidth="1"/>
+    <col min="15" max="15" width="4.60714285714286" customWidth="1"/>
+    <col min="16" max="16" width="11.3035714285714" customWidth="1"/>
     <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
     <col min="18" max="18" width="12.8303571428571" customWidth="1"/>
     <col min="19" max="19" width="10.8303571428571" customWidth="1"/>
     <col min="20" max="20" width="6.83035714285714" customWidth="1"/>
-    <col min="21" max="23" width="10.8303571428571" customWidth="1"/>
+    <col min="21" max="22" width="10.8303571428571" customWidth="1"/>
+    <col min="23" max="23" width="16.3660714285714" customWidth="1"/>
     <col min="24" max="24" width="8.83035714285714" customWidth="1"/>
-    <col min="25" max="25" width="18.8303571428571" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
     <col min="26" max="26" width="10.8303571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1913,26 +1849,25 @@
       <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>31</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="1"/>
       <c r="L2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1940,20 +1875,20 @@
         <v>34</v>
       </c>
       <c r="N2" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="Q2" s="1">
         <v>1</v>
       </c>
       <c r="R2" s="6">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="S2" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>35</v>
@@ -1961,16 +1896,20 @@
       <c r="U2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="V2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="X2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2" t="s">
-        <v>30</v>
+      <c r="Y2" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="Z2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:26">
@@ -1978,27 +1917,20 @@
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="G3"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="9" t="s">
-        <v>38</v>
+      <c r="I3" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J3" s="5"/>
-      <c r="K3" s="1"/>
       <c r="L3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M3"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
       <c r="R3" s="6"/>
       <c r="S3" s="7"/>
       <c r="T3" s="2"/>
@@ -2006,182 +1938,291 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3"/>
+      <c r="Y3" s="11"/>
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
       <c r="I4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4"/>
+        <v>46</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="6">
+        <v>46131</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="M4"/>
-      <c r="N4" s="2"/>
-      <c r="O4"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4" s="2"/>
-      <c r="Y4"/>
-      <c r="Z4" s="2"/>
+      <c r="Z4" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
+      <c r="C5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1"/>
       <c r="I5" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5"/>
       <c r="L5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5"/>
+        <v>51</v>
+      </c>
       <c r="N5" s="2"/>
-      <c r="O5"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="6"/>
       <c r="S5" s="7"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5"/>
-      <c r="W5"/>
       <c r="X5" s="2"/>
-      <c r="Y5"/>
+      <c r="Y5" s="11"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" s="1" customFormat="1" spans="1:26">
       <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="I6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="L6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6"/>
-      <c r="N6" s="2"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6"/>
-      <c r="Z6" s="2"/>
-    </row>
-    <row r="7" spans="1:26">
+        <v>33</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="6">
+        <v>46131</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:26">
       <c r="A7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="I7" s="9" t="s">
-        <v>49</v>
+      <c r="C7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7"/>
+      <c r="I7" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="J7" s="5"/>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M7"/>
       <c r="N7" s="2"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="O7" s="2"/>
       <c r="R7" s="6"/>
       <c r="S7" s="7"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7"/>
+      <c r="Y7" s="11"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" customFormat="1" spans="1:26">
       <c r="A8" s="2">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="I8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8"/>
-      <c r="N8" s="2"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8"/>
-      <c r="Z8" s="2"/>
-    </row>
-    <row r="9" spans="1:26">
+        <v>47</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="6">
+        <v>46131</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:26">
       <c r="A9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="I9" s="9" t="s">
-        <v>54</v>
+      <c r="C9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="I9" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="J9" s="5"/>
       <c r="L9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9"/>
+        <v>51</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -2190,34 +2231,34 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="X9" s="2"/>
-      <c r="Y9"/>
+      <c r="Y9" s="11"/>
       <c r="Z9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:26">
       <c r="A10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
-        <v>56</v>
+      <c r="F10" s="10" t="s">
+        <v>61</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>57</v>
+      <c r="I10" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>33</v>
@@ -2226,20 +2267,20 @@
         <v>34</v>
       </c>
       <c r="N10" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
       </c>
       <c r="R10" s="6">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="S10" s="7">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>35</v>
@@ -2247,34 +2288,37 @@
       <c r="U10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
+      <c r="V10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="X10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Y10" t="s">
-        <v>30</v>
+      <c r="Y10" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="Z10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:26">
       <c r="A11" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="10"/>
+      <c r="C11" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="G11"/>
-      <c r="I11" s="9" t="s">
-        <v>59</v>
+      <c r="I11" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="J11" s="5"/>
       <c r="L11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M11"/>
       <c r="N11" s="2"/>
@@ -2286,50 +2330,94 @@
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
-      <c r="Y11"/>
+      <c r="Y11" s="11"/>
       <c r="Z11" s="2"/>
     </row>
     <row r="12" customFormat="1" spans="1:26">
       <c r="A12" s="2">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" s="6">
+        <v>46131</v>
+      </c>
+      <c r="S12" s="7">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="I12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="L12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Z12" s="2"/>
     </row>
     <row r="13" customFormat="1" spans="1:26">
       <c r="A13" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="I13" s="9" t="s">
-        <v>61</v>
+      <c r="C13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="I13" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="J13" s="5"/>
       <c r="L13" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="N13" s="2"/>
       <c r="P13" s="1"/>
@@ -2341,626 +2429,511 @@
       <c r="X13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" customFormat="1" spans="1:26">
-      <c r="A14" s="2">
-        <v>2</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="I14" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="5"/>
-      <c r="L14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Z14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:26">
-      <c r="A15" s="2">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="I15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="L15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Z15" s="2"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:26">
-      <c r="A16" s="2">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="I16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="5"/>
-      <c r="L16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Z16" s="2"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:26">
-      <c r="A17" s="2">
-        <v>2</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="I17" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="5"/>
-      <c r="L17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Z17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:26">
-      <c r="A18" s="2">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" t="s">
-        <v>34</v>
-      </c>
-      <c r="N18" s="2">
-        <v>2</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="1">
-        <v>1000</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>1</v>
-      </c>
-      <c r="R18" s="6">
-        <v>46127</v>
-      </c>
-      <c r="S18" s="7">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:26">
-      <c r="A19" s="2">
-        <v>3</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="G19"/>
-      <c r="I19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="L19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19"/>
-      <c r="Z19" s="2"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:26">
-      <c r="A20" s="2">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="I20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="5"/>
-      <c r="L20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Z20" s="2"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:26">
-      <c r="A21" s="2">
-        <v>3</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="I21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J21" s="5"/>
-      <c r="L21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Z21" s="2"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:26">
-      <c r="A22" s="2">
-        <v>3</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="I22" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="L22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Z22" s="2"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:26">
-      <c r="A23" s="2">
-        <v>3</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="I23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="5"/>
-      <c r="L23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Z23" s="2"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:26">
-      <c r="A24" s="2">
-        <v>3</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="I24" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="5"/>
-      <c r="L24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Z24" s="2"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:26">
-      <c r="A25" s="2">
-        <v>3</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="I25" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="L25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Z25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:26">
-      <c r="A26" s="2">
-        <v>4</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" t="s">
-        <v>34</v>
-      </c>
-      <c r="N26" s="2">
-        <v>2</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="1">
-        <v>1000</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>1</v>
-      </c>
-      <c r="R26" s="6">
-        <v>46127</v>
-      </c>
-      <c r="S26" s="7">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:26">
-      <c r="A27" s="2">
-        <v>4</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="G27"/>
-      <c r="I27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="L27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27"/>
-      <c r="Z27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:26">
-      <c r="A28" s="2">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="I28" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="L28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Z28" s="2"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:26">
-      <c r="A29" s="2">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="I29" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J29" s="5"/>
-      <c r="L29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Z29" s="2"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:26">
-      <c r="A30" s="2">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="I30" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="5"/>
-      <c r="L30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Z30" s="2"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:26">
-      <c r="A31" s="2">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="I31" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="L31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Z31" s="2"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:26">
-      <c r="A32" s="2">
-        <v>4</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="I32" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J32" s="5"/>
-      <c r="L32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Z32" s="2"/>
-    </row>
-    <row r="33" customFormat="1" spans="1:26">
-      <c r="A33" s="2">
-        <v>4</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="10"/>
-      <c r="I33" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="L33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Z33" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:Z1" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Z13"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="4.75892857142857" customWidth="1"/>
+    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
+    <col min="3" max="3" width="28.5625" customWidth="1"/>
+    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="9.36607142857143" customWidth="1"/>
+    <col min="6" max="6" width="16.8303571428571" customWidth="1"/>
+    <col min="7" max="7" width="12.8303571428571" customWidth="1"/>
+    <col min="8" max="8" width="10.1071428571429" customWidth="1"/>
+    <col min="9" max="9" width="38.6785714285714" customWidth="1"/>
+    <col min="10" max="10" width="14.8303571428571" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
+    <col min="12" max="12" width="27.2321428571429" customWidth="1"/>
+    <col min="13" max="13" width="9.07142857142857" customWidth="1"/>
+    <col min="14" max="14" width="5.20535714285714" customWidth="1"/>
+    <col min="15" max="15" width="4.60714285714286" customWidth="1"/>
+    <col min="16" max="16" width="11.3035714285714" customWidth="1"/>
+    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
+    <col min="18" max="18" width="12.8303571428571" customWidth="1"/>
+    <col min="19" max="19" width="10.8303571428571" customWidth="1"/>
+    <col min="20" max="20" width="6.83035714285714" customWidth="1"/>
+    <col min="21" max="22" width="10.8303571428571" customWidth="1"/>
+    <col min="23" max="23" width="16.3660714285714" customWidth="1"/>
+    <col min="24" max="24" width="8.83035714285714" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="10.8303571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:26">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1">
+        <v>2000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="6">
+        <v>46132</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:26">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3"/>
+      <c r="I3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="6">
+        <v>46132</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="I5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="L5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:26">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="5"/>
+      <c r="L6" s="2"/>
+      <c r="M6"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:26">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="10"/>
+      <c r="G7"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="5"/>
+      <c r="L7" s="2"/>
+      <c r="M7"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:26">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="5"/>
+      <c r="L8" s="2"/>
+      <c r="M8"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:26">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="1"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="5"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:26">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="5"/>
+      <c r="L10" s="2"/>
+      <c r="M10"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:26">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="10"/>
+      <c r="G11"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="5"/>
+      <c r="L11" s="2"/>
+      <c r="M11"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:26">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="5"/>
+      <c r="L12" s="2"/>
+      <c r="M12"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:26">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="1"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="5"/>
+      <c r="L13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z43"/>
@@ -3079,24 +3052,18 @@
         <v>26</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="F2" s="9"/>
       <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>88</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="5"/>
       <c r="L2" s="2" t="s">
         <v>33</v>
       </c>
@@ -3104,7 +3071,7 @@
         <v>34</v>
       </c>
       <c r="N2" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="1">
@@ -3131,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="2">
         <v>2</v>
@@ -3143,16 +3110,14 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="D3" s="1"/>
       <c r="G3"/>
-      <c r="I3" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="I3" s="9"/>
       <c r="J3" s="5"/>
       <c r="L3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M3"/>
       <c r="N3" s="2"/>
@@ -3173,15 +3138,13 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="I4" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="I4" s="9"/>
       <c r="J4" s="5"/>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N4" s="2"/>
       <c r="P4" s="1"/>
@@ -3199,15 +3162,13 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="I5" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="5"/>
       <c r="L5" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="N5" s="2"/>
       <c r="P5" s="1"/>
@@ -3225,15 +3186,13 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="I6" s="9" t="s">
-        <v>92</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="I6" s="9"/>
       <c r="J6" s="5"/>
       <c r="L6" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="N6" s="2"/>
       <c r="P6" s="1"/>
@@ -3251,15 +3210,13 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="I7" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="5"/>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2"/>
       <c r="P7" s="1"/>
@@ -3277,15 +3234,13 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="I8" s="9" t="s">
-        <v>94</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="5"/>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N8" s="2"/>
       <c r="P8" s="1"/>
@@ -3303,15 +3258,13 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="I9" s="9" t="s">
-        <v>95</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="5"/>
       <c r="L9" s="2" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="N9" s="2"/>
       <c r="P9" s="1"/>
@@ -3331,32 +3284,26 @@
         <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
-        <v>98</v>
-      </c>
+      <c r="F10" s="9"/>
       <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>88</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="5"/>
       <c r="L10" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="M10" t="s">
         <v>34</v>
       </c>
       <c r="N10" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="1">
@@ -3383,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z10" s="2">
         <v>2</v>
@@ -3395,15 +3342,13 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="I11" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="5"/>
       <c r="L11" s="2" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N11" s="2"/>
       <c r="P11" s="1"/>
@@ -3420,13 +3365,11 @@
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>105</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I12" s="9"/>
       <c r="L12" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -3434,13 +3377,11 @@
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>108</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I13" s="9"/>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -3448,13 +3389,11 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>111</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I14" s="9"/>
       <c r="L14" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -3462,13 +3401,11 @@
         <v>2</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>114</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I15" s="9"/>
       <c r="L15" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:26">
@@ -3479,24 +3416,18 @@
         <v>26</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="9"/>
-      <c r="F16" s="9" t="s">
-        <v>116</v>
-      </c>
+      <c r="F16" s="9"/>
       <c r="G16" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="5"/>
       <c r="L16" s="2" t="s">
         <v>33</v>
       </c>
@@ -3504,7 +3435,7 @@
         <v>34</v>
       </c>
       <c r="N16" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" s="1">
@@ -3531,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z16" s="2">
         <v>2</v>
@@ -3543,16 +3474,14 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="D17" s="1"/>
       <c r="G17"/>
-      <c r="I17" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="I17" s="9"/>
       <c r="J17" s="5"/>
       <c r="L17" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M17"/>
       <c r="N17" s="2"/>
@@ -3573,15 +3502,13 @@
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="I18" s="9" t="s">
-        <v>120</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="5"/>
       <c r="L18" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N18" s="2"/>
       <c r="P18" s="1"/>
@@ -3599,15 +3526,13 @@
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="I19" s="9" t="s">
-        <v>121</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="I19" s="9"/>
       <c r="J19" s="5"/>
       <c r="L19" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="N19" s="2"/>
       <c r="P19" s="1"/>
@@ -3625,15 +3550,13 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="I20" s="9" t="s">
-        <v>122</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="5"/>
       <c r="L20" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="N20" s="2"/>
       <c r="P20" s="1"/>
@@ -3651,15 +3574,13 @@
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="I21" s="9" t="s">
-        <v>123</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="I21" s="9"/>
       <c r="J21" s="5"/>
       <c r="L21" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N21" s="2"/>
       <c r="P21" s="1"/>
@@ -3677,15 +3598,13 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="I22" s="9" t="s">
-        <v>124</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="I22" s="9"/>
       <c r="J22" s="5"/>
       <c r="L22" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N22" s="2"/>
       <c r="P22" s="1"/>
@@ -3703,15 +3622,13 @@
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="I23" s="9" t="s">
-        <v>125</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="I23" s="9"/>
       <c r="J23" s="5"/>
       <c r="L23" s="2" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="N23" s="2"/>
       <c r="P23" s="1"/>
@@ -3731,32 +3648,26 @@
         <v>26</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="E24" s="9"/>
-      <c r="F24" s="9" t="s">
-        <v>126</v>
-      </c>
+      <c r="F24" s="9"/>
       <c r="G24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="5"/>
       <c r="L24" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="M24" t="s">
         <v>34</v>
       </c>
       <c r="N24" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="1">
@@ -3783,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z24" s="2">
         <v>2</v>
@@ -3795,15 +3706,13 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="I25" s="9" t="s">
-        <v>128</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="5"/>
       <c r="L25" s="2" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N25" s="2"/>
       <c r="P25" s="1"/>
@@ -3820,13 +3729,11 @@
         <v>4</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>129</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I26" s="9"/>
       <c r="L26" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:26">
@@ -3834,13 +3741,11 @@
         <v>4</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>130</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I27" s="9"/>
       <c r="L27" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:26">
@@ -3848,13 +3753,11 @@
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>131</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I28" s="9"/>
       <c r="L28" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:26">
@@ -3862,13 +3765,11 @@
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>132</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I29" s="9"/>
       <c r="L29" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:26">
@@ -3879,24 +3780,18 @@
         <v>26</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="9"/>
-      <c r="F30" s="9" t="s">
-        <v>133</v>
-      </c>
+      <c r="F30" s="9"/>
       <c r="G30" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>135</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="5"/>
       <c r="L30" s="2" t="s">
         <v>33</v>
       </c>
@@ -3904,7 +3799,7 @@
         <v>34</v>
       </c>
       <c r="N30" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="1">
@@ -3931,7 +3826,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z30" s="2">
         <v>2</v>
@@ -3943,16 +3838,14 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="D31" s="1"/>
       <c r="G31"/>
-      <c r="I31" s="9" t="s">
-        <v>136</v>
-      </c>
+      <c r="I31" s="9"/>
       <c r="J31" s="5"/>
       <c r="L31" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M31"/>
       <c r="N31" s="2"/>
@@ -3973,15 +3866,13 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="I32" s="9" t="s">
-        <v>137</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="I32" s="9"/>
       <c r="J32" s="5"/>
       <c r="L32" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N32" s="2"/>
       <c r="P32" s="1"/>
@@ -3999,15 +3890,13 @@
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="10"/>
-      <c r="I33" s="9" t="s">
-        <v>138</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="5"/>
       <c r="L33" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="N33" s="2"/>
       <c r="P33" s="1"/>
@@ -4025,15 +3914,13 @@
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="10"/>
-      <c r="I34" s="9" t="s">
-        <v>139</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="5"/>
       <c r="L34" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="N34" s="2"/>
       <c r="P34" s="1"/>
@@ -4051,15 +3938,13 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="I35" s="9" t="s">
-        <v>140</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="5"/>
       <c r="L35" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N35" s="2"/>
       <c r="P35" s="1"/>
@@ -4077,15 +3962,13 @@
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="I36" s="9" t="s">
-        <v>141</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="I36" s="9"/>
       <c r="J36" s="5"/>
       <c r="L36" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="N36" s="2"/>
       <c r="P36" s="1"/>
@@ -4103,15 +3986,13 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="I37" s="9" t="s">
-        <v>142</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="I37" s="9"/>
       <c r="J37" s="5"/>
       <c r="L37" s="2" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="N37" s="2"/>
       <c r="P37" s="1"/>
@@ -4131,32 +4012,26 @@
         <v>26</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="E38" s="9"/>
-      <c r="F38" s="9" t="s">
-        <v>143</v>
-      </c>
+      <c r="F38" s="9"/>
       <c r="G38" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>135</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I38" s="9"/>
+      <c r="J38" s="5"/>
       <c r="L38" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="M38" t="s">
         <v>34</v>
       </c>
       <c r="N38" s="2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="1">
@@ -4183,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z38" s="2">
         <v>2</v>
@@ -4195,15 +4070,13 @@
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="10"/>
-      <c r="I39" s="9" t="s">
-        <v>145</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="I39" s="9"/>
       <c r="J39" s="5"/>
       <c r="L39" s="2" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N39" s="2"/>
       <c r="P39" s="1"/>
@@ -4220,13 +4093,11 @@
         <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>146</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I40" s="9"/>
       <c r="L40" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:26">
@@ -4234,13 +4105,11 @@
         <v>6</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>147</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="I41" s="9"/>
       <c r="L41" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:26">
@@ -4248,13 +4117,11 @@
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>148</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I42" s="9"/>
       <c r="L42" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:26">
@@ -4262,13 +4129,11 @@
         <v>6</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>149</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I43" s="9"/>
       <c r="L43" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -4277,7 +4142,1144 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Z33"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="1" width="6.83035714285714" customWidth="1"/>
+    <col min="2" max="2" width="8.83035714285714" customWidth="1"/>
+    <col min="3" max="3" width="28.5625" customWidth="1"/>
+    <col min="4" max="4" width="12.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="18.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="16.8303571428571" customWidth="1"/>
+    <col min="7" max="7" width="12.8303571428571" customWidth="1"/>
+    <col min="8" max="8" width="14.8303571428571" customWidth="1"/>
+    <col min="9" max="9" width="30.8303571428571" customWidth="1"/>
+    <col min="10" max="10" width="14.8303571428571" customWidth="1"/>
+    <col min="11" max="11" width="22.8303571428571" customWidth="1"/>
+    <col min="12" max="12" width="35.8303571428571" customWidth="1"/>
+    <col min="13" max="13" width="10.8303571428571" customWidth="1"/>
+    <col min="14" max="15" width="8.83035714285714" customWidth="1"/>
+    <col min="16" max="16" width="21.7232142857143" customWidth="1"/>
+    <col min="17" max="17" width="6.83035714285714" customWidth="1"/>
+    <col min="18" max="18" width="12.8303571428571" customWidth="1"/>
+    <col min="19" max="19" width="10.8303571428571" customWidth="1"/>
+    <col min="20" max="20" width="6.83035714285714" customWidth="1"/>
+    <col min="21" max="23" width="10.8303571428571" customWidth="1"/>
+    <col min="24" max="24" width="8.83035714285714" customWidth="1"/>
+    <col min="25" max="25" width="18.8303571428571" customWidth="1"/>
+    <col min="26" max="26" width="10.8303571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:26">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S2" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:26">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="I4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="I5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="L5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="I6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="L6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="I7" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="L7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="I8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="L8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="I9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="L9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:26">
+      <c r="A10" s="2">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:26">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="G11"/>
+      <c r="I11" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="L11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:26">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="I12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="L12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:26">
+      <c r="A13" s="2">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="I13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="L13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:26">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="I14" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="L14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:26">
+      <c r="A15" s="2">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="I15" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="L15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:26">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="I16" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="L16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:26">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="I17" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="L17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Z17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:26">
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" t="s">
+        <v>34</v>
+      </c>
+      <c r="N18" s="2">
+        <v>2</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>1</v>
+      </c>
+      <c r="R18" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:26">
+      <c r="A19" s="2">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="G19"/>
+      <c r="I19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="L19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19"/>
+      <c r="Z19" s="2"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:26">
+      <c r="A20" s="2">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="I20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="L20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Z20" s="2"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:26">
+      <c r="A21" s="2">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="I21" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="L21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Z21" s="2"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:26">
+      <c r="A22" s="2">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="I22" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="L22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Z22" s="2"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:26">
+      <c r="A23" s="2">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="I23" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="L23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Z23" s="2"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:26">
+      <c r="A24" s="2">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="I24" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="L24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Z24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:26">
+      <c r="A25" s="2">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="I25" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="L25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Z25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:26">
+      <c r="A26" s="2">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="2">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>1</v>
+      </c>
+      <c r="R26" s="6">
+        <v>46127</v>
+      </c>
+      <c r="S26" s="7">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:26">
+      <c r="A27" s="2">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="G27"/>
+      <c r="I27" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="5"/>
+      <c r="L27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:26">
+      <c r="A28" s="2">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="I28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J28" s="5"/>
+      <c r="L28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Z28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:26">
+      <c r="A29" s="2">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="I29" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="L29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Z29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:26">
+      <c r="A30" s="2">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="I30" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="L30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Z30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:26">
+      <c r="A31" s="2">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="I31" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J31" s="5"/>
+      <c r="L31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Z31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:26">
+      <c r="A32" s="2">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="I32" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="5"/>
+      <c r="L32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Z32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:26">
+      <c r="A33" s="2">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="I33" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="L33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Z33" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Z1" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z11"/>
@@ -4396,25 +5398,25 @@
         <v>26</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M2" t="s">
         <v>34</v>
@@ -4447,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="2">
         <v>1</v>
@@ -4461,25 +5463,25 @@
         <v>26</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
@@ -4512,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z3" s="2">
         <v>1</v>
@@ -4526,25 +5528,25 @@
         <v>26</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M4" t="s">
         <v>34</v>
@@ -4574,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z4" s="2">
         <v>1</v>
@@ -4588,25 +5590,25 @@
         <v>26</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M5" t="s">
         <v>34</v>
@@ -4636,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z5" s="2">
         <v>1</v>
@@ -4650,25 +5652,25 @@
         <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
@@ -4698,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z6" s="2">
         <v>1</v>
@@ -4712,25 +5714,25 @@
         <v>26</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
@@ -4760,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z7" s="2">
         <v>1</v>
@@ -4774,25 +5776,25 @@
         <v>26</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s">
         <v>34</v>
@@ -4822,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z8" s="2">
         <v>1</v>
@@ -4836,25 +5838,25 @@
         <v>26</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s">
         <v>34</v>
@@ -4884,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z9" s="2">
         <v>1</v>
@@ -4894,7 +5896,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="D10" s="1"/>
       <c r="F10" s="8"/>
       <c r="I10" s="9"/>
       <c r="J10" s="5"/>
@@ -4913,7 +5915,7 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
+      <c r="D11" s="1"/>
       <c r="F11" s="8"/>
       <c r="I11" s="9"/>
       <c r="J11" s="5"/>
@@ -4934,7 +5936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z9"/>
@@ -5050,28 +6052,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M2" t="s">
         <v>34</v>
@@ -5104,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="2">
         <v>1</v>
@@ -5115,28 +6117,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
@@ -5169,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z3" s="2">
         <v>1</v>
@@ -5180,28 +6182,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M4" t="s">
         <v>34</v>
@@ -5231,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z4" s="2">
         <v>1</v>
@@ -5242,28 +6244,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M5" t="s">
         <v>34</v>
@@ -5293,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z5" s="2">
         <v>1</v>
@@ -5304,28 +6306,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
@@ -5355,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z6" s="2">
         <v>1</v>
@@ -5366,28 +6368,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
@@ -5417,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z7" s="2">
         <v>1</v>
@@ -5428,28 +6430,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s">
         <v>34</v>
@@ -5479,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z8" s="2">
         <v>1</v>
@@ -5490,28 +6492,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s">
         <v>34</v>
@@ -5541,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z9" s="2">
         <v>1</v>
@@ -5553,7 +6555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Z3"/>
@@ -5669,25 +6671,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>33</v>
@@ -5722,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z2" s="2">
         <v>2</v>
@@ -5733,25 +6735,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
@@ -5787,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Z3" s="2">
         <v>2</v>
@@ -5799,7 +6801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D27"/>
@@ -5813,16 +6815,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5830,13 +6832,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5844,10 +6846,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -5858,13 +6860,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5872,10 +6874,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -5886,13 +6888,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5900,13 +6902,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5914,13 +6916,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5928,13 +6930,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5942,13 +6944,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5956,13 +6958,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5970,13 +6972,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5984,13 +6986,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5998,10 +7000,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
@@ -6012,13 +7014,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6026,13 +7028,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6040,13 +7042,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" t="s">
         <v>195</v>
-      </c>
-      <c r="D17" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -6054,13 +7056,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -6068,13 +7070,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6082,13 +7084,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6096,10 +7098,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
         <v>35</v>
@@ -6110,13 +7112,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6124,13 +7126,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6138,13 +7140,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6152,13 +7154,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6166,13 +7168,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C26" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6180,13 +7182,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D27" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
